--- a/results/01_pollution_assessment/HZD_Toxicity/tables/hzd_chemical_effects.xlsx
+++ b/results/01_pollution_assessment/HZD_Toxicity/tables/hzd_chemical_effects.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K234"/>
+  <dimension ref="A1:K311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>003ABC</t>
+          <t>DR-02</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -525,7 +525,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>004ABC</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -562,7 +562,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>005ABC</t>
+          <t>DR-04</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -599,7 +599,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>007ABC</t>
+          <t>DR-06</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -636,7 +636,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>008A</t>
+          <t>DR-07</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -673,7 +673,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>009B</t>
+          <t>DR-08</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -710,7 +710,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>010B</t>
+          <t>DR-09</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -747,7 +747,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>DR-10</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -784,7 +784,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>012A</t>
+          <t>DR-21</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -821,7 +821,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>013A</t>
+          <t>DR-32</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -858,7 +858,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>014B</t>
+          <t>DR-43</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -895,7 +895,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>015C</t>
+          <t>DR-54</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -932,7 +932,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>DR-65</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -969,7 +969,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>017B</t>
+          <t>DR-76</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1006,7 +1006,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>018A</t>
+          <t>DR-87</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1043,7 +1043,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>019B</t>
+          <t>DR-98</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1080,7 +1080,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>021B</t>
+          <t>DR-109</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1117,7 +1117,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>022B</t>
+          <t>DR-120</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1154,7 +1154,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>023C</t>
+          <t>DR-131</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1191,7 +1191,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>024C</t>
+          <t>DR-142</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1228,7 +1228,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>025B</t>
+          <t>DR-153</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1265,7 +1265,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>DR-160</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1302,7 +1302,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>027B</t>
+          <t>DR-161</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1339,7 +1339,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>029C</t>
+          <t>DR-163</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1376,7 +1376,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>DR-164</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1413,7 +1413,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>031A</t>
+          <t>DR-165</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1450,7 +1450,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>DR-167</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1487,7 +1487,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>034C</t>
+          <t>DR-168</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1524,7 +1524,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>DR-169</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1561,7 +1561,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>DR-170</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1598,7 +1598,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>037B</t>
+          <t>DR-171</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1635,7 +1635,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>042C</t>
+          <t>DR-175</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1672,7 +1672,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>043ABC</t>
+          <t>DR-176</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1709,7 +1709,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>044A</t>
+          <t>DR-177</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1746,7 +1746,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>045B</t>
+          <t>DR-178</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1783,7 +1783,7 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>047ABC</t>
+          <t>DR-180</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1820,7 +1820,7 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>048C</t>
+          <t>DR-181</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1857,7 +1857,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>049A</t>
+          <t>DR-182</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1894,7 +1894,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>052B</t>
+          <t>DR-184</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1931,7 +1931,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>054B</t>
+          <t>DR-186</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1968,7 +1968,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>055C</t>
+          <t>DR-187</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -2005,7 +2005,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>057C</t>
+          <t>DR-188</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2042,7 +2042,7 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>DR-189</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2079,7 +2079,7 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>059ABC</t>
+          <t>DR-190</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2116,7 +2116,7 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>DR-191</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -2153,7 +2153,7 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>DR-193</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2190,7 +2190,7 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>065C</t>
+          <t>DR-194</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -2227,7 +2227,7 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>DR-195</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2264,7 +2264,7 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>067B</t>
+          <t>DR-196</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -2301,7 +2301,7 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>DR-197</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2338,7 +2338,7 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>069A</t>
+          <t>DR-198</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -2375,7 +2375,7 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>070B</t>
+          <t>DR-199</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2412,7 +2412,7 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>DR-200</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -2449,7 +2449,7 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>072A</t>
+          <t>DR-201</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2486,7 +2486,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>DR-202</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -2523,7 +2523,7 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>074B</t>
+          <t>DR-203</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2560,7 +2560,7 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>075A</t>
+          <t>DR-204</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -2597,7 +2597,7 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>076ABC</t>
+          <t>DR-205</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2634,7 +2634,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>077B</t>
+          <t>DR-206</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -2671,7 +2671,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>078B</t>
+          <t>DR-207</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -2708,7 +2708,7 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>079C</t>
+          <t>DR-208</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -2745,7 +2745,7 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>080C</t>
+          <t>DR-209</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -2782,7 +2782,7 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>081B</t>
+          <t>DR-210</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -2819,7 +2819,7 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>082A</t>
+          <t>DR-211</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -2856,7 +2856,7 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>083B</t>
+          <t>DR-212</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -2893,7 +2893,7 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>084A</t>
+          <t>DR-213</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -2930,7 +2930,7 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>085C</t>
+          <t>DR-214</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -2967,7 +2967,7 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>086A</t>
+          <t>DR-215</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3004,7 +3004,7 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>088C</t>
+          <t>DR-216</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -3041,7 +3041,7 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>089A</t>
+          <t>DR-217</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3078,7 +3078,7 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>090B</t>
+          <t>DR-218</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -3115,7 +3115,7 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>091C</t>
+          <t>DR-219</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3152,7 +3152,7 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>092ABC</t>
+          <t>DR-220</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -3189,7 +3189,7 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>093C</t>
+          <t>DR-221</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3226,7 +3226,7 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>DR-222</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -3263,7 +3263,7 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>095A</t>
+          <t>DR-223</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3300,7 +3300,7 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>096A</t>
+          <t>DR-224</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -3337,7 +3337,7 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>097ABC</t>
+          <t>DR-225</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3374,7 +3374,7 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>098C</t>
+          <t>DR-226</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -3411,7 +3411,7 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>099C</t>
+          <t>DR-227</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -3448,7 +3448,7 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>100C</t>
+          <t>DR-228</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -3485,7 +3485,7 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>101C</t>
+          <t>DR-229</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -3522,7 +3522,7 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>102B</t>
+          <t>DR-230</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -3559,7 +3559,7 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>103A</t>
+          <t>DR-231</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -3596,7 +3596,7 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>104C</t>
+          <t>DR-232</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -3633,7 +3633,7 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>105C</t>
+          <t>DR-233</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -3670,7 +3670,7 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>106B</t>
+          <t>DR-234</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -3707,7 +3707,7 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>107C</t>
+          <t>DR-235</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -3744,7 +3744,7 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>108B</t>
+          <t>DR-11</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -3781,7 +3781,7 @@
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>DR-12</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -3818,7 +3818,7 @@
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">111C </t>
+          <t>DR-13</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -3831,56 +3831,56 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>26.53435855220197</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>8.350704125349878</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>32.5780561305631</v>
       </c>
       <c r="H92" t="n">
-        <v>100</v>
+        <v>21.33378480130806</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>7.90304394386134</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>99.8423452350427</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>12.92296319431937</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>113B</t>
+          <t>DR-15</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>6.402353055709356</v>
+        <v>0</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>14.15564031013736</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>10.71936992009084</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>7.92204755684216</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
         <v>100</v>
       </c>
       <c r="I93" t="n">
-        <v>28.84090726069413</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -3892,32 +3892,32 @@
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>114B</t>
+          <t>DR-16</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>6.551715228012524</v>
+        <v>0</v>
       </c>
       <c r="C94" t="n">
-        <v>16.70578200201015</v>
+        <v>6.402353055709356</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>5.591450511666045</v>
+        <v>14.15564031013736</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>10.71936992009084</v>
       </c>
       <c r="G94" t="n">
-        <v>6.71183492441479</v>
+        <v>7.92204755684216</v>
       </c>
       <c r="H94" t="n">
         <v>100</v>
       </c>
       <c r="I94" t="n">
-        <v>17.72123373768193</v>
+        <v>28.84090726069413</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -3929,32 +3929,32 @@
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>115ABC</t>
+          <t>DR-17</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>8.033175293677189</v>
+        <v>6.551715228012524</v>
       </c>
       <c r="C95" t="n">
-        <v>6.068429832283059</v>
+        <v>16.70578200201015</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>5.591450511666045</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>6.71183492441479</v>
       </c>
       <c r="H95" t="n">
         <v>100</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>17.72123373768193</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -3966,20 +3966,20 @@
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>116B</t>
+          <t>DR-18</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>5.200344235235507</v>
+        <v>8.033175293677189</v>
       </c>
       <c r="C96" t="n">
-        <v>6.830328197640281</v>
+        <v>6.068429832283059</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>5.64389209371202</v>
+        <v>0</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -3991,7 +3991,7 @@
         <v>100</v>
       </c>
       <c r="I96" t="n">
-        <v>5.120320600097126</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -4003,20 +4003,20 @@
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>117ABC</t>
+          <t>DR-19</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>5.753774500025409</v>
+        <v>5.200344235235507</v>
       </c>
       <c r="C97" t="n">
-        <v>8.628665014492986</v>
+        <v>6.830328197640281</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>5.64389209371202</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
@@ -4028,7 +4028,7 @@
         <v>100</v>
       </c>
       <c r="I97" t="n">
-        <v>6.993640661590074</v>
+        <v>5.120320600097126</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -4040,14 +4040,14 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>118A</t>
+          <t>DR-20</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>6.193687579469914</v>
+        <v>5.753774500025409</v>
       </c>
       <c r="C98" t="n">
-        <v>9.917106716947806</v>
+        <v>8.628665014492986</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
@@ -4065,7 +4065,7 @@
         <v>100</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>6.993640661590074</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -4077,14 +4077,14 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>119B</t>
+          <t>DR-22</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>18.01774000579202</v>
+        <v>6.193687579469914</v>
       </c>
       <c r="C99" t="n">
-        <v>19.33864173052355</v>
+        <v>9.917106716947806</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -4114,14 +4114,14 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>DR-23</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>18.01774000579202</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>19.33864173052355</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -4151,7 +4151,7 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>DR-24</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4188,7 +4188,7 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>123A</t>
+          <t>DR-25</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>5.700853414281232</v>
+        <v>0</v>
       </c>
       <c r="F102" t="n">
         <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>7.261233917279085</v>
+        <v>0</v>
       </c>
       <c r="H102" t="n">
         <v>100</v>
@@ -4225,7 +4225,7 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>124A</t>
+          <t>DR-26</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -4238,19 +4238,19 @@
         <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>5.645896461563469</v>
+        <v>5.700853414281232</v>
       </c>
       <c r="F103" t="n">
         <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>7.65941760386888</v>
+        <v>7.261233917279085</v>
       </c>
       <c r="H103" t="n">
         <v>100</v>
       </c>
       <c r="I103" t="n">
-        <v>5.10647198323028</v>
+        <v>0</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -4262,7 +4262,7 @@
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>DR-27</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -4275,19 +4275,19 @@
         <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>5.645896461563469</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>7.65941760386888</v>
       </c>
       <c r="H104" t="n">
         <v>100</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>5.10647198323028</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -4299,32 +4299,32 @@
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>126A</t>
+          <t>DR-28</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>6.624072824092957</v>
+        <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>7.278350490329725</v>
+        <v>0</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>9.88982243778899</v>
+        <v>0</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>7.29997611453525</v>
+        <v>0</v>
       </c>
       <c r="H105" t="n">
         <v>100</v>
       </c>
       <c r="I105" t="n">
-        <v>10.06229616981337</v>
+        <v>0</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -4336,32 +4336,32 @@
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>127B</t>
+          <t>DR-29</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0</v>
+        <v>6.624072824092957</v>
       </c>
       <c r="C106" t="n">
-        <v>5.317330401293617</v>
+        <v>7.278350490329725</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>0</v>
+        <v>9.88982243778899</v>
       </c>
       <c r="F106" t="n">
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>7.29997611453525</v>
       </c>
       <c r="H106" t="n">
         <v>100</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>10.06229616981337</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -4373,20 +4373,20 @@
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>128B</t>
+          <t>DR-30</t>
         </is>
       </c>
       <c r="B107" t="n">
         <v>0</v>
       </c>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>5.317330401293617</v>
       </c>
       <c r="D107" t="n">
-        <v>41.73613582259932</v>
+        <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>8.021699411844008</v>
+        <v>0</v>
       </c>
       <c r="F107" t="n">
         <v>0</v>
@@ -4410,7 +4410,7 @@
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>129A</t>
+          <t>DR-31</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -4420,10 +4420,10 @@
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>25.40602163642219</v>
+        <v>41.73613582259932</v>
       </c>
       <c r="E108" t="n">
-        <v>6.621362542397129</v>
+        <v>8.021699411844008</v>
       </c>
       <c r="F108" t="n">
         <v>0</v>
@@ -4447,7 +4447,7 @@
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>130A</t>
+          <t>DR-33</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -4457,16 +4457,16 @@
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>25.40602163642219</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>6.621362542397129</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>7.846269209144271</v>
+        <v>0</v>
       </c>
       <c r="H109" t="n">
         <v>100</v>
@@ -4484,7 +4484,7 @@
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>131B</t>
+          <t>DR-34</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -4497,31 +4497,31 @@
         <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>5.248791319288897</v>
+        <v>15.67598786711216</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>15.46331947062053</v>
       </c>
       <c r="G110" t="n">
-        <v>6.280685977380514</v>
+        <v>85.57843183483867</v>
       </c>
       <c r="H110" t="n">
-        <v>100</v>
+        <v>97.84245347492281</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>19.27203796443385</v>
       </c>
       <c r="J110" t="n">
-        <v>0</v>
+        <v>99.9999991526921</v>
       </c>
       <c r="K110" t="n">
-        <v>0</v>
+        <v>33.4434218045501</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>132B</t>
+          <t>DR-35</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -4531,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>8.958385683660957</v>
+        <v>0</v>
       </c>
       <c r="E111" t="n">
         <v>0</v>
@@ -4540,7 +4540,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>7.846269209144271</v>
       </c>
       <c r="H111" t="n">
         <v>100</v>
@@ -4558,7 +4558,7 @@
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>DR-36</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -4571,13 +4571,13 @@
         <v>0</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>5.248791319288897</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>6.280685977380514</v>
       </c>
       <c r="H112" t="n">
         <v>100</v>
@@ -4595,7 +4595,7 @@
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>134C</t>
+          <t>DR-37</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -4605,10 +4605,10 @@
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>20.14561493955718</v>
+        <v>8.958385683660957</v>
       </c>
       <c r="E113" t="n">
-        <v>6.500954750437539</v>
+        <v>0</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
@@ -4632,20 +4632,20 @@
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>135A</t>
+          <t>DR-38</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>85.60676862133595</v>
+        <v>0</v>
       </c>
       <c r="C114" t="n">
-        <v>92.15524994626531</v>
+        <v>0</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>5.640711814417968</v>
+        <v>0</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>136B</t>
+          <t>DR-39</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -4679,10 +4679,10 @@
         <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>28.65278102665946</v>
+        <v>20.14561493955718</v>
       </c>
       <c r="E115" t="n">
-        <v>9.156026847548175</v>
+        <v>6.500954750437539</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
@@ -4706,20 +4706,20 @@
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>137A</t>
+          <t>DR-40</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>85.60676862133595</v>
       </c>
       <c r="C116" t="n">
-        <v>0</v>
+        <v>92.15524994626531</v>
       </c>
       <c r="D116" t="n">
-        <v>12.78248683561289</v>
+        <v>0</v>
       </c>
       <c r="E116" t="n">
-        <v>6.744370158067412</v>
+        <v>5.640711814417968</v>
       </c>
       <c r="F116" t="n">
         <v>0</v>
@@ -4743,32 +4743,32 @@
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>138B</t>
+          <t>DR-41</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>6.263989106416716</v>
+        <v>0</v>
       </c>
       <c r="C117" t="n">
-        <v>8.046021532876493</v>
+        <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>0</v>
+        <v>28.65278102665946</v>
       </c>
       <c r="E117" t="n">
-        <v>47.13603983125662</v>
+        <v>9.156026847548175</v>
       </c>
       <c r="F117" t="n">
-        <v>19.46753161366176</v>
+        <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>12.94629708159882</v>
+        <v>0</v>
       </c>
       <c r="H117" t="n">
         <v>100</v>
       </c>
       <c r="I117" t="n">
-        <v>65.77922459723436</v>
+        <v>0</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -4780,20 +4780,20 @@
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>DR-42</t>
         </is>
       </c>
       <c r="B118" t="n">
         <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>6.103130725822679</v>
+        <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
+        <v>12.78248683561289</v>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>6.744370158067412</v>
       </c>
       <c r="F118" t="n">
         <v>0</v>
@@ -4817,32 +4817,32 @@
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>140C</t>
+          <t>DR-44</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0</v>
+        <v>6.263989106416716</v>
       </c>
       <c r="C119" t="n">
-        <v>5.485424893439013</v>
+        <v>8.046021532876493</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>36.67526729978234</v>
+        <v>47.13603983125662</v>
       </c>
       <c r="F119" t="n">
-        <v>16.5939390156138</v>
+        <v>19.46753161366176</v>
       </c>
       <c r="G119" t="n">
-        <v>12.92986063302516</v>
+        <v>12.94629708159882</v>
       </c>
       <c r="H119" t="n">
         <v>100</v>
       </c>
       <c r="I119" t="n">
-        <v>47.9170257084869</v>
+        <v>65.77922459723436</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -4854,32 +4854,32 @@
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>141B</t>
+          <t>DR-45</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>5.71388049349556</v>
+        <v>0</v>
       </c>
       <c r="C120" t="n">
-        <v>7.653114056744286</v>
+        <v>6.103130725822679</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>6.265545394908499</v>
+        <v>0</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>5.901688351245091</v>
+        <v>0</v>
       </c>
       <c r="H120" t="n">
         <v>100</v>
       </c>
       <c r="I120" t="n">
-        <v>5.228538253064097</v>
+        <v>0</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -4891,69 +4891,69 @@
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>142C</t>
+          <t>DR-46</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>5.553659073045112</v>
+        <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>5.613707897522708</v>
+        <v>0</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>6.013769815592701</v>
+        <v>6.205483585682408</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>14.90246307774164</v>
       </c>
       <c r="G121" t="n">
-        <v>8.199840850273404</v>
+        <v>62.87104040151434</v>
       </c>
       <c r="H121" t="n">
-        <v>100</v>
+        <v>85.89764766286041</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>9.724443281258141</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>99.99352216767164</v>
       </c>
       <c r="K121" t="n">
-        <v>0</v>
+        <v>20.01902199260299</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>143B</t>
+          <t>DR-47</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>5.119877839199567</v>
+        <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>7.637878342799838</v>
+        <v>5.485424893439013</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
       </c>
       <c r="E122" t="n">
-        <v>5.450693137819325</v>
+        <v>36.67526729978234</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>16.5939390156138</v>
       </c>
       <c r="G122" t="n">
-        <v>5.674014218418289</v>
+        <v>12.92986063302516</v>
       </c>
       <c r="H122" t="n">
         <v>100</v>
       </c>
       <c r="I122" t="n">
-        <v>11.73757419838878</v>
+        <v>47.9170257084869</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -4965,32 +4965,32 @@
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>144B</t>
+          <t>DR-48</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>8.326380060869202</v>
+        <v>5.71388049349556</v>
       </c>
       <c r="C123" t="n">
-        <v>21.260023964531</v>
+        <v>7.653114056744286</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
       </c>
       <c r="E123" t="n">
-        <v>8.518009966252839</v>
+        <v>6.265545394908499</v>
       </c>
       <c r="F123" t="n">
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>5.776056012508718</v>
+        <v>5.901688351245091</v>
       </c>
       <c r="H123" t="n">
         <v>100</v>
       </c>
       <c r="I123" t="n">
-        <v>11.21931988726014</v>
+        <v>5.228538253064097</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -5002,26 +5002,26 @@
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>145B</t>
+          <t>DR-49</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>6.371160153100351</v>
+        <v>5.553659073045112</v>
       </c>
       <c r="C124" t="n">
-        <v>7.867003989696516</v>
+        <v>5.613707897522708</v>
       </c>
       <c r="D124" t="n">
-        <v>18.62950443627775</v>
+        <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>7.534159189143181</v>
+        <v>6.013769815592701</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>8.199840850273404</v>
       </c>
       <c r="H124" t="n">
         <v>100</v>
@@ -5039,32 +5039,32 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>146B</t>
+          <t>DR-50</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>8.29700457208676</v>
+        <v>5.119877839199567</v>
       </c>
       <c r="C125" t="n">
-        <v>22.50029393404984</v>
+        <v>7.637878342799838</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
       </c>
       <c r="E125" t="n">
-        <v>8.174440461917541</v>
+        <v>5.450693137819325</v>
       </c>
       <c r="F125" t="n">
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>5.631950532923257</v>
+        <v>5.674014218418289</v>
       </c>
       <c r="H125" t="n">
         <v>100</v>
       </c>
       <c r="I125" t="n">
-        <v>11.00673433535818</v>
+        <v>11.73757419838878</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -5076,32 +5076,32 @@
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>147A</t>
+          <t>DR-51</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>44.99194096563486</v>
+        <v>8.326380060869202</v>
       </c>
       <c r="C126" t="n">
-        <v>45.14470086555399</v>
+        <v>21.260023964531</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>85.71583039142197</v>
+        <v>8.518009966252839</v>
       </c>
       <c r="F126" t="n">
-        <v>61.39644600249976</v>
+        <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>54.70083941317593</v>
+        <v>5.776056012508718</v>
       </c>
       <c r="H126" t="n">
         <v>100</v>
       </c>
       <c r="I126" t="n">
-        <v>99.88365346383591</v>
+        <v>11.21931988726014</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -5113,20 +5113,20 @@
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>148B</t>
+          <t>DR-52</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>5.290889017406705</v>
+        <v>6.371160153100351</v>
       </c>
       <c r="C127" t="n">
-        <v>5.891632084682794</v>
+        <v>7.867003989696516</v>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
+        <v>18.62950443627775</v>
       </c>
       <c r="E127" t="n">
-        <v>6.921848718924554</v>
+        <v>7.534159189143181</v>
       </c>
       <c r="F127" t="n">
         <v>0</v>
@@ -5138,7 +5138,7 @@
         <v>100</v>
       </c>
       <c r="I127" t="n">
-        <v>8.564622457607097</v>
+        <v>0</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -5150,32 +5150,32 @@
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>149C</t>
+          <t>DR-53</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0</v>
+        <v>8.29700457208676</v>
       </c>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>22.50029393404984</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>5.338132665276198</v>
+        <v>8.174440461917541</v>
       </c>
       <c r="F128" t="n">
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>5.627540379531546</v>
+        <v>5.631950532923257</v>
       </c>
       <c r="H128" t="n">
         <v>100</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>11.00673433535818</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -5187,32 +5187,32 @@
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>150B</t>
+          <t>DR-55</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>6.277686953006128</v>
+        <v>44.99194096563486</v>
       </c>
       <c r="C129" t="n">
-        <v>41.36421133655699</v>
+        <v>45.14470086555399</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
       </c>
       <c r="E129" t="n">
-        <v>5.96805415211417</v>
+        <v>85.71583039142197</v>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>61.39644600249976</v>
       </c>
       <c r="G129" t="n">
-        <v>5.488841954359604</v>
+        <v>54.70083941317593</v>
       </c>
       <c r="H129" t="n">
         <v>100</v>
       </c>
       <c r="I129" t="n">
-        <v>21.141972258748</v>
+        <v>99.88365346383591</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -5224,20 +5224,20 @@
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>DR-56</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0</v>
+        <v>5.290889017406705</v>
       </c>
       <c r="C130" t="n">
-        <v>0</v>
+        <v>5.891632084682794</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
       </c>
       <c r="E130" t="n">
-        <v>0</v>
+        <v>6.921848718924554</v>
       </c>
       <c r="F130" t="n">
         <v>0</v>
@@ -5246,10 +5246,10 @@
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>8.564622457607097</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -5261,7 +5261,7 @@
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>A23</t>
+          <t>DR-57</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -5274,16 +5274,16 @@
         <v>0</v>
       </c>
       <c r="E131" t="n">
-        <v>0</v>
+        <v>5.338132665276198</v>
       </c>
       <c r="F131" t="n">
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>5.627540379531546</v>
       </c>
       <c r="H131" t="n">
-        <v>8.884823624232311</v>
+        <v>100</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
@@ -5298,7 +5298,7 @@
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>DR-58</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -5317,7 +5317,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>5.293785584565371</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -5326,7 +5326,7 @@
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
+        <v>10.23296368713692</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -5335,32 +5335,32 @@
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>DR-59</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0</v>
+        <v>6.277686953006128</v>
       </c>
       <c r="C133" t="n">
-        <v>0</v>
+        <v>41.36421133655699</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>0</v>
+        <v>5.96805415211417</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>5.488841954359604</v>
       </c>
       <c r="H133" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I133" t="n">
-        <v>0</v>
+        <v>21.141972258748</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -5372,7 +5372,7 @@
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>A29</t>
+          <t>DR-60</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -5385,31 +5385,31 @@
         <v>0</v>
       </c>
       <c r="E134" t="n">
-        <v>0</v>
+        <v>71.10121043257833</v>
       </c>
       <c r="F134" t="n">
-        <v>5.204546428550801</v>
+        <v>22.04326467187206</v>
       </c>
       <c r="G134" t="n">
-        <v>6.815486280570338</v>
+        <v>38.30724157589461</v>
       </c>
       <c r="H134" t="n">
-        <v>9.159445026219716</v>
+        <v>11.49617332087172</v>
       </c>
       <c r="I134" t="n">
-        <v>18.19912516472227</v>
+        <v>29.65032118068428</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
+        <v>94.96957407430708</v>
       </c>
       <c r="K134" t="n">
-        <v>0</v>
+        <v>56.710569434464</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>DR-61</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -5431,13 +5431,13 @@
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>0</v>
+        <v>5.675400727884027</v>
       </c>
       <c r="I135" t="n">
-        <v>0</v>
+        <v>10.76916995893672</v>
       </c>
       <c r="J135" t="n">
-        <v>0</v>
+        <v>5.508352491930188</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
@@ -5446,7 +5446,7 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>A53</t>
+          <t>DR-62</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -5459,31 +5459,31 @@
         <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>0</v>
+        <v>13.82230866870491</v>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>26.01165351437064</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>92.64313127508152</v>
       </c>
       <c r="H136" t="n">
-        <v>9.246115318539733</v>
+        <v>16.71366801785759</v>
       </c>
       <c r="I136" t="n">
-        <v>0</v>
+        <v>92.73408472213589</v>
       </c>
       <c r="J136" t="n">
-        <v>0</v>
+        <v>96.29383046567825</v>
       </c>
       <c r="K136" t="n">
-        <v>0</v>
+        <v>33.4434218045501</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>A58</t>
+          <t>DR-63</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -5505,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>41.21690915865982</v>
+        <v>0</v>
       </c>
       <c r="I137" t="n">
         <v>0</v>
@@ -5520,7 +5520,7 @@
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>DR-64</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -5530,34 +5530,34 @@
         <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>0</v>
+        <v>26.60246766270335</v>
       </c>
       <c r="E138" t="n">
-        <v>0</v>
+        <v>99.99328268185647</v>
       </c>
       <c r="F138" t="n">
-        <v>0</v>
+        <v>97.96985831568031</v>
       </c>
       <c r="G138" t="n">
-        <v>5.192854952948649</v>
+        <v>99.96812575811052</v>
       </c>
       <c r="H138" t="n">
-        <v>0</v>
+        <v>81.33945031366292</v>
       </c>
       <c r="I138" t="n">
-        <v>0</v>
+        <v>91.92987374349542</v>
       </c>
       <c r="J138" t="n">
-        <v>0</v>
+        <v>99.99999999991947</v>
       </c>
       <c r="K138" t="n">
-        <v>0</v>
+        <v>98.84733951638844</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>A66</t>
+          <t>DR-66</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -5576,25 +5576,25 @@
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>5.550982678246875</v>
       </c>
       <c r="H139" t="n">
-        <v>0</v>
+        <v>6.850758101404105</v>
       </c>
       <c r="I139" t="n">
-        <v>0</v>
+        <v>15.97889029142149</v>
       </c>
       <c r="J139" t="n">
-        <v>0</v>
+        <v>12.13197435274648</v>
       </c>
       <c r="K139" t="n">
-        <v>0</v>
+        <v>6.883680330767502</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>DBC2</t>
+          <t>DR-67</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -5607,31 +5607,31 @@
         <v>0</v>
       </c>
       <c r="E140" t="n">
-        <v>0</v>
+        <v>21.18918633258608</v>
       </c>
       <c r="F140" t="n">
-        <v>0</v>
+        <v>6.828051304650421</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>73.65854854604345</v>
       </c>
       <c r="H140" t="n">
-        <v>63.07306397379421</v>
+        <v>16.25307735636092</v>
       </c>
       <c r="I140" t="n">
-        <v>0</v>
+        <v>14.51095346187034</v>
       </c>
       <c r="J140" t="n">
-        <v>0</v>
+        <v>99.93945908579576</v>
       </c>
       <c r="K140" t="n">
-        <v>0</v>
+        <v>33.4434218045501</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>DCC2</t>
+          <t>DR-68</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -5644,19 +5644,19 @@
         <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>0</v>
+        <v>8.034194138439105</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>5.293785584565371</v>
       </c>
       <c r="H141" t="n">
-        <v>7.023559361226481</v>
+        <v>6.086812205911864</v>
       </c>
       <c r="I141" t="n">
-        <v>0</v>
+        <v>12.72978888508995</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -5668,7 +5668,7 @@
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>DCE3</t>
+          <t>DR-69</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -5681,31 +5681,31 @@
         <v>0</v>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>9.464953380728709</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>7.356868724918485</v>
       </c>
       <c r="H142" t="n">
-        <v>6.865719590384834</v>
+        <v>8.333043161363225</v>
       </c>
       <c r="I142" t="n">
-        <v>8.680561279113009</v>
+        <v>11.51941522555388</v>
       </c>
       <c r="J142" t="n">
-        <v>0</v>
+        <v>5.185202647565243</v>
       </c>
       <c r="K142" t="n">
-        <v>0</v>
+        <v>5.111504479214367</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>DJC2</t>
+          <t>DR-70</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -5715,34 +5715,34 @@
         <v>0</v>
       </c>
       <c r="D143" t="n">
-        <v>0</v>
+        <v>9.249921664546934</v>
       </c>
       <c r="E143" t="n">
-        <v>0</v>
+        <v>9.983090704969095</v>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>13.32016807682755</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>27.32618767049625</v>
       </c>
       <c r="H143" t="n">
-        <v>59.74430768299121</v>
+        <v>20.77763702986249</v>
       </c>
       <c r="I143" t="n">
-        <v>0</v>
+        <v>32.07515005090367</v>
       </c>
       <c r="J143" t="n">
-        <v>0</v>
+        <v>51.59622473385993</v>
       </c>
       <c r="K143" t="n">
-        <v>0</v>
+        <v>75.78976699754257</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>DR-71</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -5779,7 +5779,7 @@
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>MCE2</t>
+          <t>DR-72</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -5792,31 +5792,31 @@
         <v>0</v>
       </c>
       <c r="E145" t="n">
-        <v>0</v>
+        <v>11.89598769465494</v>
       </c>
       <c r="F145" t="n">
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>5.507314290633484</v>
       </c>
       <c r="H145" t="n">
-        <v>19.88353183245006</v>
+        <v>6.779926497724275</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>7.114194677478794</v>
       </c>
       <c r="J145" t="n">
-        <v>0</v>
+        <v>7.281827472979206</v>
       </c>
       <c r="K145" t="n">
-        <v>0</v>
+        <v>5.013811020590712</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>DR-73</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -5826,34 +5826,34 @@
         <v>0</v>
       </c>
       <c r="D146" t="n">
-        <v>0</v>
+        <v>5.128071429754423</v>
       </c>
       <c r="E146" t="n">
-        <v>0</v>
+        <v>6.64913987141926</v>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>12.82525108318384</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>11.85292542409929</v>
       </c>
       <c r="H146" t="n">
-        <v>0</v>
+        <v>5.000000000000001</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>19.27203796443385</v>
       </c>
       <c r="J146" t="n">
-        <v>0</v>
+        <v>17.29543801439495</v>
       </c>
       <c r="K146" t="n">
-        <v>0</v>
+        <v>33.4434218045501</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>DR-74</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -5890,7 +5890,7 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>S100</t>
+          <t>DR-75</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -5927,7 +5927,7 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>S101</t>
+          <t>DR-77</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -5940,19 +5940,19 @@
         <v>0</v>
       </c>
       <c r="E149" t="n">
-        <v>0</v>
+        <v>5.789593824180805</v>
       </c>
       <c r="F149" t="n">
         <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>64.80068922437663</v>
       </c>
       <c r="H149" t="n">
-        <v>0</v>
+        <v>22.86946914334234</v>
       </c>
       <c r="I149" t="n">
-        <v>0</v>
+        <v>12.72978888508996</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>S102</t>
+          <t>DR-78</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -5977,16 +5977,16 @@
         <v>0</v>
       </c>
       <c r="E150" t="n">
-        <v>0</v>
+        <v>6.205483585682408</v>
       </c>
       <c r="F150" t="n">
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>5.047868459659377</v>
       </c>
       <c r="H150" t="n">
-        <v>0</v>
+        <v>6.435854013458179</v>
       </c>
       <c r="I150" t="n">
         <v>0</v>
@@ -6001,7 +6001,7 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>DR-79</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -6014,31 +6014,31 @@
         <v>0</v>
       </c>
       <c r="E151" t="n">
-        <v>0</v>
+        <v>16.67634691538452</v>
       </c>
       <c r="F151" t="n">
         <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>5.958911221707874</v>
       </c>
       <c r="H151" t="n">
-        <v>46.07658715304557</v>
+        <v>13.31102705430714</v>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>14.51095346187034</v>
       </c>
       <c r="J151" t="n">
-        <v>0</v>
+        <v>5.344473562195361</v>
       </c>
       <c r="K151" t="n">
-        <v>0</v>
+        <v>5.847381136396207</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>DR-80</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -6048,34 +6048,34 @@
         <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>0</v>
+        <v>6.512668657839618</v>
       </c>
       <c r="E152" t="n">
-        <v>0</v>
+        <v>82.69929490582847</v>
       </c>
       <c r="F152" t="n">
-        <v>0</v>
+        <v>48.91125238418822</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>82.19923278194803</v>
       </c>
       <c r="H152" t="n">
-        <v>34.26612528957411</v>
+        <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>0</v>
+        <v>19.27203796443385</v>
       </c>
       <c r="J152" t="n">
-        <v>0</v>
+        <v>84.03236332019647</v>
       </c>
       <c r="K152" t="n">
-        <v>0</v>
+        <v>92.04071291623237</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>DR-81</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -6085,34 +6085,34 @@
         <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>0</v>
+        <v>5.781586978700881</v>
       </c>
       <c r="E153" t="n">
-        <v>0</v>
+        <v>62.9792638443578</v>
       </c>
       <c r="F153" t="n">
-        <v>0</v>
+        <v>48.91125238418822</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>20.1101843683256</v>
       </c>
       <c r="H153" t="n">
-        <v>0</v>
+        <v>61.50129137315776</v>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>83.71348483125379</v>
       </c>
       <c r="J153" t="n">
-        <v>0</v>
+        <v>43.64744646415021</v>
       </c>
       <c r="K153" t="n">
-        <v>0</v>
+        <v>70.67905459369923</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>DR-82</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -6128,19 +6128,19 @@
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>0</v>
+        <v>77.95673532812795</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>6.701691522744245</v>
       </c>
       <c r="H154" t="n">
-        <v>6.266701781214498</v>
+        <v>0</v>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>42.66381600921547</v>
       </c>
       <c r="J154" t="n">
-        <v>0</v>
+        <v>16.84339084204926</v>
       </c>
       <c r="K154" t="n">
         <v>0</v>
@@ -6149,7 +6149,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>DR-83</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -6171,7 +6171,7 @@
         <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>10.4822261573836</v>
+        <v>0</v>
       </c>
       <c r="I155" t="n">
         <v>0</v>
@@ -6186,7 +6186,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>DR-84</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -6196,34 +6196,34 @@
         <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>6.016291067071164</v>
       </c>
       <c r="E156" t="n">
-        <v>0</v>
+        <v>99.99999743746923</v>
       </c>
       <c r="F156" t="n">
-        <v>0</v>
+        <v>92.88958281507439</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>58.89159394689687</v>
       </c>
       <c r="H156" t="n">
-        <v>0</v>
+        <v>14.65147547520967</v>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>80.3717484521955</v>
       </c>
       <c r="J156" t="n">
-        <v>0</v>
+        <v>48.93564924777502</v>
       </c>
       <c r="K156" t="n">
-        <v>0</v>
+        <v>68.84179797708036</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>DR-85</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -6260,7 +6260,7 @@
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>DR-86</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -6279,13 +6279,13 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>5.047868459659377</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>7.114194677478794</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -6297,7 +6297,7 @@
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>DR-88</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -6334,7 +6334,7 @@
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>DR-89</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -6347,7 +6347,7 @@
         <v>0</v>
       </c>
       <c r="E160" t="n">
-        <v>0</v>
+        <v>7.625967865461954</v>
       </c>
       <c r="F160" t="n">
         <v>0</v>
@@ -6359,7 +6359,7 @@
         <v>0</v>
       </c>
       <c r="I160" t="n">
-        <v>0</v>
+        <v>5.164509848990815</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -6371,7 +6371,7 @@
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>DR-90</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -6384,31 +6384,31 @@
         <v>0</v>
       </c>
       <c r="E161" t="n">
-        <v>0</v>
+        <v>5.399972173447412</v>
       </c>
       <c r="F161" t="n">
-        <v>0</v>
+        <v>12.34610376958698</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>12.66188337597633</v>
       </c>
       <c r="H161" t="n">
-        <v>7.390458650182329</v>
+        <v>5.675400727884027</v>
       </c>
       <c r="I161" t="n">
-        <v>0</v>
+        <v>21.10271900328551</v>
       </c>
       <c r="J161" t="n">
-        <v>0</v>
+        <v>25.24096522407995</v>
       </c>
       <c r="K161" t="n">
-        <v>0</v>
+        <v>17.3742368127506</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>S21(5)</t>
+          <t>DR-91</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -6430,10 +6430,10 @@
         <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>5.684363316358896</v>
+        <v>6.922274750620015</v>
       </c>
       <c r="I162" t="n">
-        <v>0</v>
+        <v>8.183298316360426</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -6445,7 +6445,7 @@
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>DR-92</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -6458,31 +6458,31 @@
         <v>0</v>
       </c>
       <c r="E163" t="n">
-        <v>0</v>
+        <v>5.035169476035903</v>
       </c>
       <c r="F163" t="n">
-        <v>0</v>
+        <v>12.82525108318384</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>11.08908902894842</v>
       </c>
       <c r="H163" t="n">
-        <v>22.85963389508339</v>
+        <v>8.248242933000675</v>
       </c>
       <c r="I163" t="n">
-        <v>0</v>
+        <v>29.65032118068428</v>
       </c>
       <c r="J163" t="n">
-        <v>0</v>
+        <v>24.64312621203024</v>
       </c>
       <c r="K163" t="n">
-        <v>0</v>
+        <v>21.45030982521133</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>DR-93</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -6504,10 +6504,10 @@
         <v>0</v>
       </c>
       <c r="H164" t="n">
-        <v>7.247474382534291</v>
+        <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>0</v>
+        <v>6.398614500872457</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -6519,7 +6519,7 @@
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>DR-94</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -6556,7 +6556,7 @@
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>DR-95</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -6593,7 +6593,7 @@
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>DR-96</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -6606,7 +6606,7 @@
         <v>0</v>
       </c>
       <c r="E167" t="n">
-        <v>5.002804972697071</v>
+        <v>5.399972173447412</v>
       </c>
       <c r="F167" t="n">
         <v>0</v>
@@ -6615,7 +6615,7 @@
         <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>30.2839734564243</v>
+        <v>0</v>
       </c>
       <c r="I167" t="n">
         <v>0</v>
@@ -6630,7 +6630,7 @@
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>S27(5)</t>
+          <t>DR-97</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -6643,7 +6643,7 @@
         <v>0</v>
       </c>
       <c r="E168" t="n">
-        <v>0</v>
+        <v>6.64913987141926</v>
       </c>
       <c r="F168" t="n">
         <v>0</v>
@@ -6652,7 +6652,7 @@
         <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>13.42728302628974</v>
+        <v>0</v>
       </c>
       <c r="I168" t="n">
         <v>0</v>
@@ -6667,7 +6667,7 @@
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>DR-99</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -6680,31 +6680,31 @@
         <v>0</v>
       </c>
       <c r="E169" t="n">
-        <v>0</v>
+        <v>23.75845027955972</v>
       </c>
       <c r="F169" t="n">
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>7.886426333460212</v>
       </c>
       <c r="H169" t="n">
-        <v>0</v>
+        <v>8.505024873968837</v>
       </c>
       <c r="I169" t="n">
-        <v>0</v>
+        <v>9.724443281258141</v>
       </c>
       <c r="J169" t="n">
-        <v>0</v>
+        <v>5.185202647565243</v>
       </c>
       <c r="K169" t="n">
-        <v>0</v>
+        <v>8.087860648747283</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>DR-100</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -6717,7 +6717,7 @@
         <v>0</v>
       </c>
       <c r="E170" t="n">
-        <v>0</v>
+        <v>5.035169476035903</v>
       </c>
       <c r="F170" t="n">
         <v>0</v>
@@ -6726,7 +6726,7 @@
         <v>0</v>
       </c>
       <c r="H170" t="n">
-        <v>0</v>
+        <v>5.327608797529681</v>
       </c>
       <c r="I170" t="n">
         <v>0</v>
@@ -6741,7 +6741,7 @@
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>DR-101</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -6754,7 +6754,7 @@
         <v>0</v>
       </c>
       <c r="E171" t="n">
-        <v>0</v>
+        <v>7.122106511604757</v>
       </c>
       <c r="F171" t="n">
         <v>0</v>
@@ -6763,10 +6763,10 @@
         <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>5.886788765859095</v>
+        <v>5.857198868898054</v>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>5.164509848990815</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>DR-102</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -6791,31 +6791,31 @@
         <v>0</v>
       </c>
       <c r="E172" t="n">
-        <v>0</v>
+        <v>11.38995019667452</v>
       </c>
       <c r="F172" t="n">
-        <v>0</v>
+        <v>5.799605144806634</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>5.683950776161191</v>
       </c>
       <c r="H172" t="n">
-        <v>0</v>
+        <v>5.000000000000001</v>
       </c>
       <c r="I172" t="n">
-        <v>0</v>
+        <v>10.76916995893672</v>
       </c>
       <c r="J172" t="n">
-        <v>0</v>
+        <v>6.400978050851909</v>
       </c>
       <c r="K172" t="n">
-        <v>0</v>
+        <v>8.759538119120228</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>DR-103</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -6852,7 +6852,7 @@
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>DR-104</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -6865,7 +6865,7 @@
         <v>0</v>
       </c>
       <c r="E174" t="n">
-        <v>0</v>
+        <v>8.162342771205225</v>
       </c>
       <c r="F174" t="n">
         <v>0</v>
@@ -6889,7 +6889,7 @@
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>DR-105</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -6902,7 +6902,7 @@
         <v>0</v>
       </c>
       <c r="E175" t="n">
-        <v>0</v>
+        <v>10.66611152027505</v>
       </c>
       <c r="F175" t="n">
         <v>0</v>
@@ -6911,7 +6911,7 @@
         <v>0</v>
       </c>
       <c r="H175" t="n">
-        <v>0</v>
+        <v>6.850758101404105</v>
       </c>
       <c r="I175" t="n">
         <v>0</v>
@@ -6926,7 +6926,7 @@
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>DR-106</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -6939,31 +6939,31 @@
         <v>0</v>
       </c>
       <c r="E176" t="n">
-        <v>0</v>
+        <v>61.2428504376884</v>
       </c>
       <c r="F176" t="n">
-        <v>0</v>
+        <v>10.17582369911891</v>
       </c>
       <c r="G176" t="n">
-        <v>0</v>
+        <v>11.85292542409929</v>
       </c>
       <c r="H176" t="n">
-        <v>70.68192661380374</v>
+        <v>9.319373728466941</v>
       </c>
       <c r="I176" t="n">
-        <v>0</v>
+        <v>13.15675514407642</v>
       </c>
       <c r="J176" t="n">
-        <v>0</v>
+        <v>7.426883895805227</v>
       </c>
       <c r="K176" t="n">
-        <v>0</v>
+        <v>16.15897737343023</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>S40</t>
+          <t>DR-107</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -6976,7 +6976,7 @@
         <v>0</v>
       </c>
       <c r="E177" t="n">
-        <v>0</v>
+        <v>7.122106511604757</v>
       </c>
       <c r="F177" t="n">
         <v>0</v>
@@ -6985,7 +6985,7 @@
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>48.57835309873153</v>
+        <v>5.857198868898054</v>
       </c>
       <c r="I177" t="n">
         <v>0</v>
@@ -7000,7 +7000,7 @@
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>DR-108</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -7013,7 +7013,7 @@
         <v>0</v>
       </c>
       <c r="E178" t="n">
-        <v>0</v>
+        <v>6.64913987141926</v>
       </c>
       <c r="F178" t="n">
         <v>0</v>
@@ -7022,7 +7022,7 @@
         <v>0</v>
       </c>
       <c r="H178" t="n">
-        <v>5.405775384698827</v>
+        <v>0</v>
       </c>
       <c r="I178" t="n">
         <v>0</v>
@@ -7037,7 +7037,7 @@
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>DR-110</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -7050,13 +7050,13 @@
         <v>0</v>
       </c>
       <c r="E179" t="n">
-        <v>0</v>
+        <v>6.205483585682408</v>
       </c>
       <c r="F179" t="n">
         <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>5.958911221707874</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -7065,7 +7065,7 @@
         <v>0</v>
       </c>
       <c r="J179" t="n">
-        <v>0</v>
+        <v>8.856525952842702</v>
       </c>
       <c r="K179" t="n">
         <v>0</v>
@@ -7074,7 +7074,7 @@
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>DR-111</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -7084,34 +7084,34 @@
         <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>0</v>
+        <v>8.238647308978599</v>
       </c>
       <c r="E180" t="n">
-        <v>0</v>
+        <v>94.3693247179298</v>
       </c>
       <c r="F180" t="n">
-        <v>0</v>
+        <v>99.84836954335428</v>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>85.57843183483867</v>
       </c>
       <c r="H180" t="n">
-        <v>0</v>
+        <v>17.6660538094408</v>
       </c>
       <c r="I180" t="n">
-        <v>0</v>
+        <v>99.99042765071644</v>
       </c>
       <c r="J180" t="n">
-        <v>0</v>
+        <v>94.96957407430708</v>
       </c>
       <c r="K180" t="n">
-        <v>0</v>
+        <v>75.78976699754257</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>DR-112</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -7136,7 +7136,7 @@
         <v>0</v>
       </c>
       <c r="I181" t="n">
-        <v>0</v>
+        <v>5.164509848990815</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -7148,7 +7148,7 @@
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>DR-113</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -7161,31 +7161,31 @@
         <v>0</v>
       </c>
       <c r="E182" t="n">
-        <v>0</v>
+        <v>8.162342771205225</v>
       </c>
       <c r="F182" t="n">
-        <v>0</v>
+        <v>5.341606433710396</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
       </c>
       <c r="H182" t="n">
-        <v>0</v>
+        <v>12.55761391650547</v>
       </c>
       <c r="I182" t="n">
-        <v>0</v>
+        <v>13.15675514407642</v>
       </c>
       <c r="J182" t="n">
-        <v>0</v>
+        <v>6.028803046042093</v>
       </c>
       <c r="K182" t="n">
-        <v>0</v>
+        <v>17.3742368127506</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>S46</t>
+          <t>DR-114</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -7198,31 +7198,31 @@
         <v>0</v>
       </c>
       <c r="E183" t="n">
-        <v>0</v>
+        <v>32.66896920293457</v>
       </c>
       <c r="F183" t="n">
-        <v>0</v>
+        <v>29.50180221482777</v>
       </c>
       <c r="G183" t="n">
-        <v>0</v>
+        <v>8.84686919525058</v>
       </c>
       <c r="H183" t="n">
-        <v>0</v>
+        <v>19.17374499734829</v>
       </c>
       <c r="I183" t="n">
-        <v>0</v>
+        <v>74.43378310063315</v>
       </c>
       <c r="J183" t="n">
-        <v>0</v>
+        <v>13.93961073208768</v>
       </c>
       <c r="K183" t="n">
-        <v>0</v>
+        <v>64.98787793108163</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>DR-115</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -7232,34 +7232,34 @@
         <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>0</v>
+        <v>5.511289495707627</v>
       </c>
       <c r="E184" t="n">
-        <v>0</v>
+        <v>84.3889339941792</v>
       </c>
       <c r="F184" t="n">
-        <v>0</v>
+        <v>16.63664244036342</v>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
+        <v>16.15220961447156</v>
       </c>
       <c r="H184" t="n">
-        <v>0</v>
+        <v>17.1846328658357</v>
       </c>
       <c r="I184" t="n">
-        <v>0</v>
+        <v>49.24215868966861</v>
       </c>
       <c r="J184" t="n">
-        <v>0</v>
+        <v>18.871509655057</v>
       </c>
       <c r="K184" t="n">
-        <v>0</v>
+        <v>21.45030982521133</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>DR-116</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -7272,31 +7272,31 @@
         <v>0</v>
       </c>
       <c r="E185" t="n">
-        <v>0</v>
+        <v>6.64913987141926</v>
       </c>
       <c r="F185" t="n">
-        <v>0</v>
+        <v>21.3038958991423</v>
       </c>
       <c r="G185" t="n">
-        <v>0</v>
+        <v>22.6367073017696</v>
       </c>
       <c r="H185" t="n">
-        <v>0</v>
+        <v>99.99999999999996</v>
       </c>
       <c r="I185" t="n">
-        <v>0</v>
+        <v>32.07515005090367</v>
       </c>
       <c r="J185" t="n">
-        <v>0</v>
+        <v>22.90747265500721</v>
       </c>
       <c r="K185" t="n">
-        <v>0</v>
+        <v>27.89777405855625</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>DR-117</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -7309,31 +7309,31 @@
         <v>0</v>
       </c>
       <c r="E186" t="n">
-        <v>0</v>
+        <v>9.339235642419547</v>
       </c>
       <c r="F186" t="n">
-        <v>0</v>
+        <v>5.341606433710396</v>
       </c>
       <c r="G186" t="n">
-        <v>0</v>
+        <v>9.259813555738546</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
       </c>
       <c r="I186" t="n">
-        <v>0</v>
+        <v>19.27203796443385</v>
       </c>
       <c r="J186" t="n">
-        <v>0</v>
+        <v>14.32715258570361</v>
       </c>
       <c r="K186" t="n">
-        <v>0</v>
+        <v>9.481242657679211</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>DR-118</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -7343,34 +7343,34 @@
         <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>0</v>
+        <v>7.329004538950965</v>
       </c>
       <c r="E187" t="n">
-        <v>5.120534266644658</v>
+        <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>0</v>
+        <v>48.91125238418822</v>
       </c>
       <c r="G187" t="n">
-        <v>0</v>
+        <v>21.34622345984546</v>
       </c>
       <c r="H187" t="n">
-        <v>99.55203235569968</v>
+        <v>12.19478496253049</v>
       </c>
       <c r="I187" t="n">
-        <v>0</v>
+        <v>48.29538733426625</v>
       </c>
       <c r="J187" t="n">
-        <v>0</v>
+        <v>84.03236332019647</v>
       </c>
       <c r="K187" t="n">
-        <v>0</v>
+        <v>98.63096175261306</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>DR-119</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -7383,31 +7383,31 @@
         <v>0</v>
       </c>
       <c r="E188" t="n">
-        <v>0</v>
+        <v>62.9792638443578</v>
       </c>
       <c r="F188" t="n">
-        <v>0</v>
+        <v>48.91125238418822</v>
       </c>
       <c r="G188" t="n">
-        <v>0</v>
+        <v>44.38074866758192</v>
       </c>
       <c r="H188" t="n">
-        <v>0</v>
+        <v>99.9998117779236</v>
       </c>
       <c r="I188" t="n">
-        <v>0</v>
+        <v>74.43378310063315</v>
       </c>
       <c r="J188" t="n">
-        <v>0</v>
+        <v>59.46504956793056</v>
       </c>
       <c r="K188" t="n">
-        <v>0</v>
+        <v>29.68330607633967</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>DR-121</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -7429,10 +7429,10 @@
         <v>0</v>
       </c>
       <c r="H189" t="n">
-        <v>0</v>
+        <v>93.69716891990706</v>
       </c>
       <c r="I189" t="n">
-        <v>0</v>
+        <v>7.36871341140629</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -7444,7 +7444,7 @@
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>DR-122</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -7457,31 +7457,31 @@
         <v>0</v>
       </c>
       <c r="E190" t="n">
-        <v>0</v>
+        <v>98.83702037518515</v>
       </c>
       <c r="F190" t="n">
-        <v>0</v>
+        <v>36.21052778188851</v>
       </c>
       <c r="G190" t="n">
-        <v>0</v>
+        <v>99.99292036605331</v>
       </c>
       <c r="H190" t="n">
-        <v>0</v>
+        <v>99.94444163201338</v>
       </c>
       <c r="I190" t="n">
-        <v>0</v>
+        <v>51.13665316148636</v>
       </c>
       <c r="J190" t="n">
-        <v>0</v>
+        <v>99.99999999999669</v>
       </c>
       <c r="K190" t="n">
-        <v>0</v>
+        <v>52.3937919767344</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>DR-123</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -7518,7 +7518,7 @@
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>SCR-01</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -7555,7 +7555,7 @@
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>LSC-01</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -7577,7 +7577,7 @@
         <v>0</v>
       </c>
       <c r="H193" t="n">
-        <v>5.720346834762566</v>
+        <v>8.884823624232311</v>
       </c>
       <c r="I193" t="n">
         <v>0</v>
@@ -7592,7 +7592,7 @@
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>S56</t>
+          <t>LSC-02</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -7629,7 +7629,7 @@
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>S57</t>
+          <t>LSC-03</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -7651,7 +7651,7 @@
         <v>0</v>
       </c>
       <c r="H195" t="n">
-        <v>44.46845182625755</v>
+        <v>0</v>
       </c>
       <c r="I195" t="n">
         <v>0</v>
@@ -7666,7 +7666,7 @@
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>S58</t>
+          <t>LSC-04</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -7682,16 +7682,16 @@
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>0</v>
+        <v>5.204546428550801</v>
       </c>
       <c r="G196" t="n">
-        <v>0</v>
+        <v>6.815486280570338</v>
       </c>
       <c r="H196" t="n">
-        <v>6.213844945247019</v>
+        <v>9.159445026219716</v>
       </c>
       <c r="I196" t="n">
-        <v>0</v>
+        <v>18.19912516472227</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>SCR-02</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -7725,7 +7725,7 @@
         <v>0</v>
       </c>
       <c r="H197" t="n">
-        <v>7.727072983155174</v>
+        <v>0</v>
       </c>
       <c r="I197" t="n">
         <v>0</v>
@@ -7740,7 +7740,7 @@
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>S60</t>
+          <t>LSC-05</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -7762,7 +7762,7 @@
         <v>0</v>
       </c>
       <c r="H198" t="n">
-        <v>11.83054525377548</v>
+        <v>9.246115318539733</v>
       </c>
       <c r="I198" t="n">
         <v>0</v>
@@ -7777,7 +7777,7 @@
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>S61</t>
+          <t>LSC-06</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -7799,7 +7799,7 @@
         <v>0</v>
       </c>
       <c r="H199" t="n">
-        <v>12.92588204574501</v>
+        <v>41.21690915865982</v>
       </c>
       <c r="I199" t="n">
         <v>0</v>
@@ -7814,7 +7814,7 @@
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>S62</t>
+          <t>SCR-03</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -7833,10 +7833,10 @@
         <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>0</v>
+        <v>5.192854952948649</v>
       </c>
       <c r="H200" t="n">
-        <v>7.587488221961018</v>
+        <v>0</v>
       </c>
       <c r="I200" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>S63</t>
+          <t>LSC-07</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -7888,7 +7888,7 @@
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>S64</t>
+          <t>DR-124</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -7901,7 +7901,7 @@
         <v>0</v>
       </c>
       <c r="E202" t="n">
-        <v>0</v>
+        <v>5.399972173447412</v>
       </c>
       <c r="F202" t="n">
         <v>0</v>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="I202" t="n">
-        <v>0</v>
+        <v>9.724443281258141</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -7925,7 +7925,7 @@
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>S65</t>
+          <t>DR-125</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -7950,10 +7950,10 @@
         <v>0</v>
       </c>
       <c r="I203" t="n">
-        <v>0</v>
+        <v>5.164509848990815</v>
       </c>
       <c r="J203" t="n">
-        <v>0</v>
+        <v>21.25957634287237</v>
       </c>
       <c r="K203" t="n">
         <v>0</v>
@@ -7962,7 +7962,7 @@
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>S66</t>
+          <t>DR-126</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -7984,7 +7984,7 @@
         <v>0</v>
       </c>
       <c r="H204" t="n">
-        <v>0</v>
+        <v>5.327608797529681</v>
       </c>
       <c r="I204" t="n">
         <v>0</v>
@@ -7999,7 +7999,7 @@
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>S67</t>
+          <t>LSC-08</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -8021,7 +8021,7 @@
         <v>0</v>
       </c>
       <c r="H205" t="n">
-        <v>0</v>
+        <v>63.07306397379421</v>
       </c>
       <c r="I205" t="n">
         <v>0</v>
@@ -8036,7 +8036,7 @@
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>S68</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -8058,7 +8058,7 @@
         <v>0</v>
       </c>
       <c r="H206" t="n">
-        <v>0</v>
+        <v>7.023559361226481</v>
       </c>
       <c r="I206" t="n">
         <v>0</v>
@@ -8073,7 +8073,7 @@
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>S69</t>
+          <t>LSC-10</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -8095,10 +8095,10 @@
         <v>0</v>
       </c>
       <c r="H207" t="n">
-        <v>0</v>
+        <v>6.865719590384834</v>
       </c>
       <c r="I207" t="n">
-        <v>0</v>
+        <v>8.680561279113009</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -8110,7 +8110,7 @@
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>S70</t>
+          <t>LSC-11</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -8132,7 +8132,7 @@
         <v>0</v>
       </c>
       <c r="H208" t="n">
-        <v>0</v>
+        <v>59.74430768299121</v>
       </c>
       <c r="I208" t="n">
         <v>0</v>
@@ -8147,7 +8147,7 @@
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>S72</t>
+          <t>DR-127</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -8184,7 +8184,7 @@
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>S74</t>
+          <t>DR-128</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -8197,31 +8197,31 @@
         <v>0</v>
       </c>
       <c r="E210" t="n">
-        <v>0</v>
+        <v>7.625967865461954</v>
       </c>
       <c r="F210" t="n">
-        <v>0</v>
+        <v>7.110417184925621</v>
       </c>
       <c r="G210" t="n">
-        <v>0</v>
+        <v>44.38074866758192</v>
       </c>
       <c r="H210" t="n">
-        <v>0</v>
+        <v>99.9999999999456</v>
       </c>
       <c r="I210" t="n">
-        <v>0</v>
+        <v>14.51095346187034</v>
       </c>
       <c r="J210" t="n">
-        <v>0</v>
+        <v>99.99657976392068</v>
       </c>
       <c r="K210" t="n">
-        <v>0</v>
+        <v>18.66054968633708</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>S78</t>
+          <t>DR-129</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -8258,7 +8258,7 @@
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>S79</t>
+          <t>LSC-12</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -8295,7 +8295,7 @@
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>DR-130</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -8332,7 +8332,7 @@
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>S80</t>
+          <t>DR-132</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -8354,7 +8354,7 @@
         <v>0</v>
       </c>
       <c r="H214" t="n">
-        <v>6.681902749466157</v>
+        <v>5.675400727884027</v>
       </c>
       <c r="I214" t="n">
         <v>0</v>
@@ -8369,7 +8369,7 @@
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>S81</t>
+          <t>DR-133</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -8406,7 +8406,7 @@
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>S82</t>
+          <t>DR-134</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -8431,10 +8431,10 @@
         <v>0</v>
       </c>
       <c r="I216" t="n">
-        <v>0</v>
+        <v>5.164509848990815</v>
       </c>
       <c r="J216" t="n">
-        <v>0</v>
+        <v>23.47632266930842</v>
       </c>
       <c r="K216" t="n">
         <v>0</v>
@@ -8443,7 +8443,7 @@
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>S83</t>
+          <t>DR-135</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -8456,31 +8456,31 @@
         <v>0</v>
       </c>
       <c r="E217" t="n">
-        <v>0</v>
+        <v>9.339235642419547</v>
       </c>
       <c r="F217" t="n">
         <v>0</v>
       </c>
       <c r="G217" t="n">
-        <v>5.740685340517458</v>
+        <v>5.293785584565371</v>
       </c>
       <c r="H217" t="n">
-        <v>5.833259838663818</v>
+        <v>10.51366430173782</v>
       </c>
       <c r="I217" t="n">
-        <v>0</v>
+        <v>13.15675514407642</v>
       </c>
       <c r="J217" t="n">
-        <v>22.66026809938682</v>
+        <v>0</v>
       </c>
       <c r="K217" t="n">
-        <v>0</v>
+        <v>5.847381136396207</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>S84</t>
+          <t>DR-136</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -8499,13 +8499,13 @@
         <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>6.552707723218681</v>
+        <v>0</v>
       </c>
       <c r="H218" t="n">
-        <v>7.256476420011278</v>
+        <v>0</v>
       </c>
       <c r="I218" t="n">
-        <v>10.78009929167267</v>
+        <v>0</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -8517,44 +8517,44 @@
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>S85</t>
+          <t>LSC-13</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>6.988924732145268</v>
+        <v>0</v>
       </c>
       <c r="C219" t="n">
-        <v>5.757897275492518</v>
+        <v>0</v>
       </c>
       <c r="D219" t="n">
         <v>0</v>
       </c>
       <c r="E219" t="n">
-        <v>14.92069081914642</v>
+        <v>0</v>
       </c>
       <c r="F219" t="n">
-        <v>13.08557375006232</v>
+        <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>26.6344660655082</v>
+        <v>0</v>
       </c>
       <c r="H219" t="n">
-        <v>99.99999754550056</v>
+        <v>19.88353183245006</v>
       </c>
       <c r="I219" t="n">
-        <v>12.47105442941014</v>
+        <v>0</v>
       </c>
       <c r="J219" t="n">
-        <v>76.63822623815099</v>
+        <v>0</v>
       </c>
       <c r="K219" t="n">
-        <v>6.979213733923796</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>S87</t>
+          <t>DR-137</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -8573,13 +8573,13 @@
         <v>0</v>
       </c>
       <c r="G220" t="n">
-        <v>5.327838802008446</v>
+        <v>0</v>
       </c>
       <c r="H220" t="n">
-        <v>0</v>
+        <v>5.161347102684794</v>
       </c>
       <c r="I220" t="n">
-        <v>0</v>
+        <v>5.164509848990815</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -8591,44 +8591,44 @@
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>S89</t>
+          <t>DR-138</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>7.262820876455278</v>
+        <v>0</v>
       </c>
       <c r="C221" t="n">
         <v>0</v>
       </c>
       <c r="D221" t="n">
-        <v>0</v>
+        <v>32.76401423426789</v>
       </c>
       <c r="E221" t="n">
-        <v>0</v>
+        <v>96.64357537135236</v>
       </c>
       <c r="F221" t="n">
-        <v>0</v>
+        <v>77.95673532812795</v>
       </c>
       <c r="G221" t="n">
-        <v>7.132729141377689</v>
+        <v>34.44037940401095</v>
       </c>
       <c r="H221" t="n">
-        <v>13.95706888936943</v>
+        <v>99.28232402856395</v>
       </c>
       <c r="I221" t="n">
-        <v>12.62073359058132</v>
+        <v>84.72059049980676</v>
       </c>
       <c r="J221" t="n">
-        <v>0</v>
+        <v>90.8822775391864</v>
       </c>
       <c r="K221" t="n">
-        <v>0</v>
+        <v>53.83994019397183</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>DR-139</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -8641,7 +8641,7 @@
         <v>0</v>
       </c>
       <c r="E222" t="n">
-        <v>0</v>
+        <v>6.205483585682408</v>
       </c>
       <c r="F222" t="n">
         <v>0</v>
@@ -8650,10 +8650,10 @@
         <v>0</v>
       </c>
       <c r="H222" t="n">
-        <v>0</v>
+        <v>5.000000000000001</v>
       </c>
       <c r="I222" t="n">
-        <v>0</v>
+        <v>5.164509848990815</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -8665,14 +8665,14 @@
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>S90</t>
+          <t>SCR-04</t>
         </is>
       </c>
       <c r="B223" t="n">
         <v>0</v>
       </c>
       <c r="C223" t="n">
-        <v>8.594946353211522</v>
+        <v>0</v>
       </c>
       <c r="D223" t="n">
         <v>0</v>
@@ -8681,28 +8681,28 @@
         <v>0</v>
       </c>
       <c r="F223" t="n">
-        <v>19.08736886554397</v>
+        <v>0</v>
       </c>
       <c r="G223" t="n">
-        <v>84.4279250692869</v>
+        <v>0</v>
       </c>
       <c r="H223" t="n">
-        <v>10.6402502289721</v>
+        <v>0</v>
       </c>
       <c r="I223" t="n">
-        <v>22.79647838284913</v>
+        <v>0</v>
       </c>
       <c r="J223" t="n">
-        <v>78.30960864053299</v>
+        <v>0</v>
       </c>
       <c r="K223" t="n">
-        <v>24.85533963257184</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>S93</t>
+          <t>SCR-10</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -8721,13 +8721,13 @@
         <v>0</v>
       </c>
       <c r="G224" t="n">
-        <v>5.83504792787634</v>
+        <v>0</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
       </c>
       <c r="I224" t="n">
-        <v>15.15717672903713</v>
+        <v>0</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -8739,7 +8739,7 @@
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>S94</t>
+          <t>DR-140</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -8758,13 +8758,13 @@
         <v>0</v>
       </c>
       <c r="G225" t="n">
-        <v>5.98284898440956</v>
+        <v>0</v>
       </c>
       <c r="H225" t="n">
-        <v>9.378923733705561</v>
+        <v>0</v>
       </c>
       <c r="I225" t="n">
-        <v>6.892093174697115</v>
+        <v>0</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -8776,7 +8776,7 @@
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>S95</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -8798,7 +8798,7 @@
         <v>0</v>
       </c>
       <c r="H226" t="n">
-        <v>5.091373116196439</v>
+        <v>0</v>
       </c>
       <c r="I226" t="n">
         <v>0</v>
@@ -8813,7 +8813,7 @@
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>S96</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -8850,7 +8850,7 @@
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>S97</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -8872,7 +8872,7 @@
         <v>0</v>
       </c>
       <c r="H228" t="n">
-        <v>0</v>
+        <v>46.07658715304557</v>
       </c>
       <c r="I228" t="n">
         <v>0</v>
@@ -8887,7 +8887,7 @@
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>S98</t>
+          <t>SCR-12</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -8900,31 +8900,31 @@
         <v>0</v>
       </c>
       <c r="E229" t="n">
-        <v>14.03463143926563</v>
+        <v>0</v>
       </c>
       <c r="F229" t="n">
-        <v>12.09844426801691</v>
+        <v>0</v>
       </c>
       <c r="G229" t="n">
-        <v>9.775918907971436</v>
+        <v>0</v>
       </c>
       <c r="H229" t="n">
-        <v>10.32008274953751</v>
+        <v>34.26612528957411</v>
       </c>
       <c r="I229" t="n">
-        <v>27.88032223917946</v>
+        <v>0</v>
       </c>
       <c r="J229" t="n">
-        <v>6.88604263071726</v>
+        <v>0</v>
       </c>
       <c r="K229" t="n">
-        <v>11.99230886438421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>S99</t>
+          <t>SCR-13</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -8946,7 +8946,7 @@
         <v>0</v>
       </c>
       <c r="H230" t="n">
-        <v>5.405775384698827</v>
+        <v>0</v>
       </c>
       <c r="I230" t="n">
         <v>0</v>
@@ -8961,7 +8961,7 @@
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>UBC1</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -8983,7 +8983,7 @@
         <v>0</v>
       </c>
       <c r="H231" t="n">
-        <v>29.60315858123303</v>
+        <v>6.266701781214498</v>
       </c>
       <c r="I231" t="n">
         <v>0</v>
@@ -8998,7 +8998,7 @@
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>UCC1</t>
+          <t>SCR-15</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -9020,7 +9020,7 @@
         <v>0</v>
       </c>
       <c r="H232" t="n">
-        <v>19.56039334862705</v>
+        <v>10.4822261573836</v>
       </c>
       <c r="I232" t="n">
         <v>0</v>
@@ -9035,7 +9035,7 @@
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>UCE1</t>
+          <t>SCR-16</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -9057,7 +9057,7 @@
         <v>0</v>
       </c>
       <c r="H233" t="n">
-        <v>6.292300746884432</v>
+        <v>0</v>
       </c>
       <c r="I233" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>UJC1</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -9094,15 +9094,2864 @@
         <v>0</v>
       </c>
       <c r="H234" t="n">
+        <v>0</v>
+      </c>
+      <c r="I234" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0</v>
+      </c>
+      <c r="K234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>SCR-18</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>0</v>
+      </c>
+      <c r="C235" t="n">
+        <v>0</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0</v>
+      </c>
+      <c r="E235" t="n">
+        <v>0</v>
+      </c>
+      <c r="F235" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0</v>
+      </c>
+      <c r="I235" t="n">
+        <v>0</v>
+      </c>
+      <c r="J235" t="n">
+        <v>0</v>
+      </c>
+      <c r="K235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>SCR-19</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>0</v>
+      </c>
+      <c r="C236" t="n">
+        <v>0</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" t="n">
+        <v>0</v>
+      </c>
+      <c r="F236" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0</v>
+      </c>
+      <c r="I236" t="n">
+        <v>0</v>
+      </c>
+      <c r="J236" t="n">
+        <v>0</v>
+      </c>
+      <c r="K236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>SCR-20</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>0</v>
+      </c>
+      <c r="C237" t="n">
+        <v>0</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0</v>
+      </c>
+      <c r="E237" t="n">
+        <v>0</v>
+      </c>
+      <c r="F237" t="n">
+        <v>0</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" t="n">
+        <v>0</v>
+      </c>
+      <c r="I237" t="n">
+        <v>0</v>
+      </c>
+      <c r="J237" t="n">
+        <v>0</v>
+      </c>
+      <c r="K237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>LSC-14</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>0</v>
+      </c>
+      <c r="C238" t="n">
+        <v>0</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0</v>
+      </c>
+      <c r="E238" t="n">
+        <v>0</v>
+      </c>
+      <c r="F238" t="n">
+        <v>0</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" t="n">
+        <v>7.390458650182329</v>
+      </c>
+      <c r="I238" t="n">
+        <v>0</v>
+      </c>
+      <c r="J238" t="n">
+        <v>0</v>
+      </c>
+      <c r="K238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>LSC-15</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>0</v>
+      </c>
+      <c r="C239" t="n">
+        <v>0</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0</v>
+      </c>
+      <c r="E239" t="n">
+        <v>0</v>
+      </c>
+      <c r="F239" t="n">
+        <v>0</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" t="n">
+        <v>5.684363316358896</v>
+      </c>
+      <c r="I239" t="n">
+        <v>0</v>
+      </c>
+      <c r="J239" t="n">
+        <v>0</v>
+      </c>
+      <c r="K239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>LSC-16</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>0</v>
+      </c>
+      <c r="C240" t="n">
+        <v>0</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" t="n">
+        <v>0</v>
+      </c>
+      <c r="F240" t="n">
+        <v>0</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="n">
+        <v>22.85963389508339</v>
+      </c>
+      <c r="I240" t="n">
+        <v>0</v>
+      </c>
+      <c r="J240" t="n">
+        <v>0</v>
+      </c>
+      <c r="K240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>LSC-17</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>0</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0</v>
+      </c>
+      <c r="E241" t="n">
+        <v>0</v>
+      </c>
+      <c r="F241" t="n">
+        <v>0</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" t="n">
+        <v>7.247474382534291</v>
+      </c>
+      <c r="I241" t="n">
+        <v>0</v>
+      </c>
+      <c r="J241" t="n">
+        <v>0</v>
+      </c>
+      <c r="K241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>LSC-18</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>0</v>
+      </c>
+      <c r="C242" t="n">
+        <v>0</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0</v>
+      </c>
+      <c r="E242" t="n">
+        <v>0</v>
+      </c>
+      <c r="F242" t="n">
+        <v>0</v>
+      </c>
+      <c r="G242" t="n">
+        <v>0</v>
+      </c>
+      <c r="H242" t="n">
+        <v>0</v>
+      </c>
+      <c r="I242" t="n">
+        <v>0</v>
+      </c>
+      <c r="J242" t="n">
+        <v>0</v>
+      </c>
+      <c r="K242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>LSC-19</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>0</v>
+      </c>
+      <c r="C243" t="n">
+        <v>0</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0</v>
+      </c>
+      <c r="E243" t="n">
+        <v>0</v>
+      </c>
+      <c r="F243" t="n">
+        <v>0</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" t="n">
+        <v>0</v>
+      </c>
+      <c r="I243" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" t="n">
+        <v>0</v>
+      </c>
+      <c r="K243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>LSC-20</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>0</v>
+      </c>
+      <c r="C244" t="n">
+        <v>0</v>
+      </c>
+      <c r="D244" t="n">
+        <v>0</v>
+      </c>
+      <c r="E244" t="n">
+        <v>5.002804972697071</v>
+      </c>
+      <c r="F244" t="n">
+        <v>0</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" t="n">
+        <v>30.2839734564243</v>
+      </c>
+      <c r="I244" t="n">
+        <v>0</v>
+      </c>
+      <c r="J244" t="n">
+        <v>0</v>
+      </c>
+      <c r="K244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>LSC-21</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>0</v>
+      </c>
+      <c r="C245" t="n">
+        <v>0</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0</v>
+      </c>
+      <c r="E245" t="n">
+        <v>0</v>
+      </c>
+      <c r="F245" t="n">
+        <v>0</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" t="n">
+        <v>13.42728302628974</v>
+      </c>
+      <c r="I245" t="n">
+        <v>0</v>
+      </c>
+      <c r="J245" t="n">
+        <v>0</v>
+      </c>
+      <c r="K245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>LSC-22</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>0</v>
+      </c>
+      <c r="C246" t="n">
+        <v>0</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0</v>
+      </c>
+      <c r="E246" t="n">
+        <v>0</v>
+      </c>
+      <c r="F246" t="n">
+        <v>0</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="n">
+        <v>0</v>
+      </c>
+      <c r="I246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>LSC-23</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>0</v>
+      </c>
+      <c r="C247" t="n">
+        <v>0</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0</v>
+      </c>
+      <c r="E247" t="n">
+        <v>0</v>
+      </c>
+      <c r="F247" t="n">
+        <v>0</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" t="n">
+        <v>0</v>
+      </c>
+      <c r="I247" t="n">
+        <v>0</v>
+      </c>
+      <c r="J247" t="n">
+        <v>0</v>
+      </c>
+      <c r="K247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>SCR-05</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>0</v>
+      </c>
+      <c r="C248" t="n">
+        <v>0</v>
+      </c>
+      <c r="D248" t="n">
+        <v>0</v>
+      </c>
+      <c r="E248" t="n">
+        <v>0</v>
+      </c>
+      <c r="F248" t="n">
+        <v>0</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" t="n">
+        <v>5.886788765859095</v>
+      </c>
+      <c r="I248" t="n">
+        <v>0</v>
+      </c>
+      <c r="J248" t="n">
+        <v>0</v>
+      </c>
+      <c r="K248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>LSC-24</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>0</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0</v>
+      </c>
+      <c r="D249" t="n">
+        <v>0</v>
+      </c>
+      <c r="E249" t="n">
+        <v>0</v>
+      </c>
+      <c r="F249" t="n">
+        <v>0</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" t="n">
+        <v>0</v>
+      </c>
+      <c r="I249" t="n">
+        <v>0</v>
+      </c>
+      <c r="J249" t="n">
+        <v>0</v>
+      </c>
+      <c r="K249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>LSC-25</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>0</v>
+      </c>
+      <c r="C250" t="n">
+        <v>0</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0</v>
+      </c>
+      <c r="E250" t="n">
+        <v>0</v>
+      </c>
+      <c r="F250" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" t="n">
+        <v>0</v>
+      </c>
+      <c r="I250" t="n">
+        <v>0</v>
+      </c>
+      <c r="J250" t="n">
+        <v>0</v>
+      </c>
+      <c r="K250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>LSC-26</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>0</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0</v>
+      </c>
+      <c r="E251" t="n">
+        <v>0</v>
+      </c>
+      <c r="F251" t="n">
+        <v>0</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" t="n">
+        <v>0</v>
+      </c>
+      <c r="I251" t="n">
+        <v>0</v>
+      </c>
+      <c r="J251" t="n">
+        <v>0</v>
+      </c>
+      <c r="K251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>LSC-27</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>0</v>
+      </c>
+      <c r="C252" t="n">
+        <v>0</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0</v>
+      </c>
+      <c r="E252" t="n">
+        <v>0</v>
+      </c>
+      <c r="F252" t="n">
+        <v>0</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" t="n">
+        <v>0</v>
+      </c>
+      <c r="I252" t="n">
+        <v>0</v>
+      </c>
+      <c r="J252" t="n">
+        <v>0</v>
+      </c>
+      <c r="K252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>SCR-06</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>0</v>
+      </c>
+      <c r="C253" t="n">
+        <v>0</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0</v>
+      </c>
+      <c r="E253" t="n">
+        <v>0</v>
+      </c>
+      <c r="F253" t="n">
+        <v>0</v>
+      </c>
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" t="n">
+        <v>70.68192661380374</v>
+      </c>
+      <c r="I253" t="n">
+        <v>0</v>
+      </c>
+      <c r="J253" t="n">
+        <v>0</v>
+      </c>
+      <c r="K253" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>LSC-28</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>0</v>
+      </c>
+      <c r="C254" t="n">
+        <v>0</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0</v>
+      </c>
+      <c r="E254" t="n">
+        <v>0</v>
+      </c>
+      <c r="F254" t="n">
+        <v>0</v>
+      </c>
+      <c r="G254" t="n">
+        <v>0</v>
+      </c>
+      <c r="H254" t="n">
+        <v>48.57835309873153</v>
+      </c>
+      <c r="I254" t="n">
+        <v>0</v>
+      </c>
+      <c r="J254" t="n">
+        <v>0</v>
+      </c>
+      <c r="K254" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>LSC-29</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>0</v>
+      </c>
+      <c r="C255" t="n">
+        <v>0</v>
+      </c>
+      <c r="D255" t="n">
+        <v>0</v>
+      </c>
+      <c r="E255" t="n">
+        <v>0</v>
+      </c>
+      <c r="F255" t="n">
+        <v>0</v>
+      </c>
+      <c r="G255" t="n">
+        <v>0</v>
+      </c>
+      <c r="H255" t="n">
+        <v>5.405775384698827</v>
+      </c>
+      <c r="I255" t="n">
+        <v>0</v>
+      </c>
+      <c r="J255" t="n">
+        <v>0</v>
+      </c>
+      <c r="K255" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>LSC-30</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>0</v>
+      </c>
+      <c r="C256" t="n">
+        <v>0</v>
+      </c>
+      <c r="D256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E256" t="n">
+        <v>0</v>
+      </c>
+      <c r="F256" t="n">
+        <v>0</v>
+      </c>
+      <c r="G256" t="n">
+        <v>0</v>
+      </c>
+      <c r="H256" t="n">
+        <v>0</v>
+      </c>
+      <c r="I256" t="n">
+        <v>0</v>
+      </c>
+      <c r="J256" t="n">
+        <v>0</v>
+      </c>
+      <c r="K256" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>LSC-31</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>0</v>
+      </c>
+      <c r="C257" t="n">
+        <v>0</v>
+      </c>
+      <c r="D257" t="n">
+        <v>0</v>
+      </c>
+      <c r="E257" t="n">
+        <v>0</v>
+      </c>
+      <c r="F257" t="n">
+        <v>0</v>
+      </c>
+      <c r="G257" t="n">
+        <v>0</v>
+      </c>
+      <c r="H257" t="n">
+        <v>0</v>
+      </c>
+      <c r="I257" t="n">
+        <v>0</v>
+      </c>
+      <c r="J257" t="n">
+        <v>0</v>
+      </c>
+      <c r="K257" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>LSC-32</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>0</v>
+      </c>
+      <c r="C258" t="n">
+        <v>0</v>
+      </c>
+      <c r="D258" t="n">
+        <v>0</v>
+      </c>
+      <c r="E258" t="n">
+        <v>0</v>
+      </c>
+      <c r="F258" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" t="n">
+        <v>0</v>
+      </c>
+      <c r="H258" t="n">
+        <v>0</v>
+      </c>
+      <c r="I258" t="n">
+        <v>0</v>
+      </c>
+      <c r="J258" t="n">
+        <v>0</v>
+      </c>
+      <c r="K258" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>LSC-33</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>0</v>
+      </c>
+      <c r="C259" t="n">
+        <v>0</v>
+      </c>
+      <c r="D259" t="n">
+        <v>0</v>
+      </c>
+      <c r="E259" t="n">
+        <v>0</v>
+      </c>
+      <c r="F259" t="n">
+        <v>0</v>
+      </c>
+      <c r="G259" t="n">
+        <v>0</v>
+      </c>
+      <c r="H259" t="n">
+        <v>0</v>
+      </c>
+      <c r="I259" t="n">
+        <v>0</v>
+      </c>
+      <c r="J259" t="n">
+        <v>0</v>
+      </c>
+      <c r="K259" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>LSC-34</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>0</v>
+      </c>
+      <c r="C260" t="n">
+        <v>0</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0</v>
+      </c>
+      <c r="E260" t="n">
+        <v>0</v>
+      </c>
+      <c r="F260" t="n">
+        <v>0</v>
+      </c>
+      <c r="G260" t="n">
+        <v>0</v>
+      </c>
+      <c r="H260" t="n">
+        <v>0</v>
+      </c>
+      <c r="I260" t="n">
+        <v>0</v>
+      </c>
+      <c r="J260" t="n">
+        <v>0</v>
+      </c>
+      <c r="K260" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>LSC-35</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>0</v>
+      </c>
+      <c r="C261" t="n">
+        <v>0</v>
+      </c>
+      <c r="D261" t="n">
+        <v>0</v>
+      </c>
+      <c r="E261" t="n">
+        <v>0</v>
+      </c>
+      <c r="F261" t="n">
+        <v>0</v>
+      </c>
+      <c r="G261" t="n">
+        <v>0</v>
+      </c>
+      <c r="H261" t="n">
+        <v>0</v>
+      </c>
+      <c r="I261" t="n">
+        <v>0</v>
+      </c>
+      <c r="J261" t="n">
+        <v>0</v>
+      </c>
+      <c r="K261" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>LSC-36</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>0</v>
+      </c>
+      <c r="C262" t="n">
+        <v>0</v>
+      </c>
+      <c r="D262" t="n">
+        <v>0</v>
+      </c>
+      <c r="E262" t="n">
+        <v>0</v>
+      </c>
+      <c r="F262" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" t="n">
+        <v>0</v>
+      </c>
+      <c r="H262" t="n">
+        <v>0</v>
+      </c>
+      <c r="I262" t="n">
+        <v>0</v>
+      </c>
+      <c r="J262" t="n">
+        <v>0</v>
+      </c>
+      <c r="K262" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>LSC-37</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>0</v>
+      </c>
+      <c r="C263" t="n">
+        <v>0</v>
+      </c>
+      <c r="D263" t="n">
+        <v>0</v>
+      </c>
+      <c r="E263" t="n">
+        <v>0</v>
+      </c>
+      <c r="F263" t="n">
+        <v>0</v>
+      </c>
+      <c r="G263" t="n">
+        <v>0</v>
+      </c>
+      <c r="H263" t="n">
+        <v>0</v>
+      </c>
+      <c r="I263" t="n">
+        <v>0</v>
+      </c>
+      <c r="J263" t="n">
+        <v>0</v>
+      </c>
+      <c r="K263" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>SCR-07</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>0</v>
+      </c>
+      <c r="C264" t="n">
+        <v>0</v>
+      </c>
+      <c r="D264" t="n">
+        <v>0</v>
+      </c>
+      <c r="E264" t="n">
+        <v>5.120534266644658</v>
+      </c>
+      <c r="F264" t="n">
+        <v>0</v>
+      </c>
+      <c r="G264" t="n">
+        <v>0</v>
+      </c>
+      <c r="H264" t="n">
+        <v>99.55203235569968</v>
+      </c>
+      <c r="I264" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" t="n">
+        <v>0</v>
+      </c>
+      <c r="K264" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>LSC-38</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>0</v>
+      </c>
+      <c r="C265" t="n">
+        <v>0</v>
+      </c>
+      <c r="D265" t="n">
+        <v>0</v>
+      </c>
+      <c r="E265" t="n">
+        <v>0</v>
+      </c>
+      <c r="F265" t="n">
+        <v>0</v>
+      </c>
+      <c r="G265" t="n">
+        <v>0</v>
+      </c>
+      <c r="H265" t="n">
+        <v>0</v>
+      </c>
+      <c r="I265" t="n">
+        <v>0</v>
+      </c>
+      <c r="J265" t="n">
+        <v>0</v>
+      </c>
+      <c r="K265" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>LSC-39</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>0</v>
+      </c>
+      <c r="C266" t="n">
+        <v>0</v>
+      </c>
+      <c r="D266" t="n">
+        <v>0</v>
+      </c>
+      <c r="E266" t="n">
+        <v>0</v>
+      </c>
+      <c r="F266" t="n">
+        <v>0</v>
+      </c>
+      <c r="G266" t="n">
+        <v>0</v>
+      </c>
+      <c r="H266" t="n">
+        <v>0</v>
+      </c>
+      <c r="I266" t="n">
+        <v>0</v>
+      </c>
+      <c r="J266" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>LSC-40</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>0</v>
+      </c>
+      <c r="C267" t="n">
+        <v>0</v>
+      </c>
+      <c r="D267" t="n">
+        <v>0</v>
+      </c>
+      <c r="E267" t="n">
+        <v>0</v>
+      </c>
+      <c r="F267" t="n">
+        <v>0</v>
+      </c>
+      <c r="G267" t="n">
+        <v>0</v>
+      </c>
+      <c r="H267" t="n">
+        <v>0</v>
+      </c>
+      <c r="I267" t="n">
+        <v>0</v>
+      </c>
+      <c r="J267" t="n">
+        <v>0</v>
+      </c>
+      <c r="K267" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>LSC-41</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>0</v>
+      </c>
+      <c r="C268" t="n">
+        <v>0</v>
+      </c>
+      <c r="D268" t="n">
+        <v>0</v>
+      </c>
+      <c r="E268" t="n">
+        <v>0</v>
+      </c>
+      <c r="F268" t="n">
+        <v>0</v>
+      </c>
+      <c r="G268" t="n">
+        <v>0</v>
+      </c>
+      <c r="H268" t="n">
+        <v>0</v>
+      </c>
+      <c r="I268" t="n">
+        <v>0</v>
+      </c>
+      <c r="J268" t="n">
+        <v>0</v>
+      </c>
+      <c r="K268" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>LSC-42</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>0</v>
+      </c>
+      <c r="C269" t="n">
+        <v>0</v>
+      </c>
+      <c r="D269" t="n">
+        <v>0</v>
+      </c>
+      <c r="E269" t="n">
+        <v>0</v>
+      </c>
+      <c r="F269" t="n">
+        <v>0</v>
+      </c>
+      <c r="G269" t="n">
+        <v>0</v>
+      </c>
+      <c r="H269" t="n">
+        <v>0</v>
+      </c>
+      <c r="I269" t="n">
+        <v>0</v>
+      </c>
+      <c r="J269" t="n">
+        <v>0</v>
+      </c>
+      <c r="K269" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>LSC-43</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>0</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0</v>
+      </c>
+      <c r="D270" t="n">
+        <v>0</v>
+      </c>
+      <c r="E270" t="n">
+        <v>0</v>
+      </c>
+      <c r="F270" t="n">
+        <v>0</v>
+      </c>
+      <c r="G270" t="n">
+        <v>0</v>
+      </c>
+      <c r="H270" t="n">
+        <v>5.720346834762566</v>
+      </c>
+      <c r="I270" t="n">
+        <v>0</v>
+      </c>
+      <c r="J270" t="n">
+        <v>0</v>
+      </c>
+      <c r="K270" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>LSC-44</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>0</v>
+      </c>
+      <c r="C271" t="n">
+        <v>0</v>
+      </c>
+      <c r="D271" t="n">
+        <v>0</v>
+      </c>
+      <c r="E271" t="n">
+        <v>0</v>
+      </c>
+      <c r="F271" t="n">
+        <v>0</v>
+      </c>
+      <c r="G271" t="n">
+        <v>0</v>
+      </c>
+      <c r="H271" t="n">
+        <v>0</v>
+      </c>
+      <c r="I271" t="n">
+        <v>0</v>
+      </c>
+      <c r="J271" t="n">
+        <v>0</v>
+      </c>
+      <c r="K271" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>LSC-45</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>0</v>
+      </c>
+      <c r="C272" t="n">
+        <v>0</v>
+      </c>
+      <c r="D272" t="n">
+        <v>0</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="n">
+        <v>0</v>
+      </c>
+      <c r="H272" t="n">
+        <v>44.46845182625755</v>
+      </c>
+      <c r="I272" t="n">
+        <v>0</v>
+      </c>
+      <c r="J272" t="n">
+        <v>0</v>
+      </c>
+      <c r="K272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>LSC-46</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>0</v>
+      </c>
+      <c r="C273" t="n">
+        <v>0</v>
+      </c>
+      <c r="D273" t="n">
+        <v>0</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="n">
+        <v>0</v>
+      </c>
+      <c r="H273" t="n">
+        <v>6.213844945247019</v>
+      </c>
+      <c r="I273" t="n">
+        <v>0</v>
+      </c>
+      <c r="J273" t="n">
+        <v>0</v>
+      </c>
+      <c r="K273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>LSC-47</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>0</v>
+      </c>
+      <c r="C274" t="n">
+        <v>0</v>
+      </c>
+      <c r="D274" t="n">
+        <v>0</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="n">
+        <v>0</v>
+      </c>
+      <c r="H274" t="n">
+        <v>7.727072983155174</v>
+      </c>
+      <c r="I274" t="n">
+        <v>0</v>
+      </c>
+      <c r="J274" t="n">
+        <v>0</v>
+      </c>
+      <c r="K274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>LSC-48</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>0</v>
+      </c>
+      <c r="C275" t="n">
+        <v>0</v>
+      </c>
+      <c r="D275" t="n">
+        <v>0</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="n">
+        <v>0</v>
+      </c>
+      <c r="H275" t="n">
+        <v>11.83054525377548</v>
+      </c>
+      <c r="I275" t="n">
+        <v>0</v>
+      </c>
+      <c r="J275" t="n">
+        <v>0</v>
+      </c>
+      <c r="K275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>LSC-49</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>0</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0</v>
+      </c>
+      <c r="D276" t="n">
+        <v>0</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="n">
+        <v>0</v>
+      </c>
+      <c r="H276" t="n">
+        <v>12.92588204574501</v>
+      </c>
+      <c r="I276" t="n">
+        <v>0</v>
+      </c>
+      <c r="J276" t="n">
+        <v>0</v>
+      </c>
+      <c r="K276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>LSC-50</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>0</v>
+      </c>
+      <c r="C277" t="n">
+        <v>0</v>
+      </c>
+      <c r="D277" t="n">
+        <v>0</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="n">
+        <v>0</v>
+      </c>
+      <c r="H277" t="n">
+        <v>7.587488221961018</v>
+      </c>
+      <c r="I277" t="n">
+        <v>0</v>
+      </c>
+      <c r="J277" t="n">
+        <v>0</v>
+      </c>
+      <c r="K277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>LSC-51</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>0</v>
+      </c>
+      <c r="C278" t="n">
+        <v>0</v>
+      </c>
+      <c r="D278" t="n">
+        <v>0</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="n">
+        <v>0</v>
+      </c>
+      <c r="H278" t="n">
+        <v>0</v>
+      </c>
+      <c r="I278" t="n">
+        <v>0</v>
+      </c>
+      <c r="J278" t="n">
+        <v>0</v>
+      </c>
+      <c r="K278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>LSC-52</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>0</v>
+      </c>
+      <c r="C279" t="n">
+        <v>0</v>
+      </c>
+      <c r="D279" t="n">
+        <v>0</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="n">
+        <v>0</v>
+      </c>
+      <c r="H279" t="n">
+        <v>0</v>
+      </c>
+      <c r="I279" t="n">
+        <v>0</v>
+      </c>
+      <c r="J279" t="n">
+        <v>0</v>
+      </c>
+      <c r="K279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>LSC-53</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>0</v>
+      </c>
+      <c r="C280" t="n">
+        <v>0</v>
+      </c>
+      <c r="D280" t="n">
+        <v>0</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="n">
+        <v>0</v>
+      </c>
+      <c r="H280" t="n">
+        <v>0</v>
+      </c>
+      <c r="I280" t="n">
+        <v>0</v>
+      </c>
+      <c r="J280" t="n">
+        <v>0</v>
+      </c>
+      <c r="K280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>LSC-54</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>0</v>
+      </c>
+      <c r="C281" t="n">
+        <v>0</v>
+      </c>
+      <c r="D281" t="n">
+        <v>0</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="n">
+        <v>0</v>
+      </c>
+      <c r="H281" t="n">
+        <v>0</v>
+      </c>
+      <c r="I281" t="n">
+        <v>0</v>
+      </c>
+      <c r="J281" t="n">
+        <v>0</v>
+      </c>
+      <c r="K281" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>LSC-55</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>0</v>
+      </c>
+      <c r="C282" t="n">
+        <v>0</v>
+      </c>
+      <c r="D282" t="n">
+        <v>0</v>
+      </c>
+      <c r="E282" t="n">
+        <v>0</v>
+      </c>
+      <c r="F282" t="n">
+        <v>0</v>
+      </c>
+      <c r="G282" t="n">
+        <v>0</v>
+      </c>
+      <c r="H282" t="n">
+        <v>0</v>
+      </c>
+      <c r="I282" t="n">
+        <v>0</v>
+      </c>
+      <c r="J282" t="n">
+        <v>0</v>
+      </c>
+      <c r="K282" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>LSC-56</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>0</v>
+      </c>
+      <c r="C283" t="n">
+        <v>0</v>
+      </c>
+      <c r="D283" t="n">
+        <v>0</v>
+      </c>
+      <c r="E283" t="n">
+        <v>0</v>
+      </c>
+      <c r="F283" t="n">
+        <v>0</v>
+      </c>
+      <c r="G283" t="n">
+        <v>0</v>
+      </c>
+      <c r="H283" t="n">
+        <v>0</v>
+      </c>
+      <c r="I283" t="n">
+        <v>0</v>
+      </c>
+      <c r="J283" t="n">
+        <v>0</v>
+      </c>
+      <c r="K283" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>LSC-57</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>0</v>
+      </c>
+      <c r="C284" t="n">
+        <v>0</v>
+      </c>
+      <c r="D284" t="n">
+        <v>0</v>
+      </c>
+      <c r="E284" t="n">
+        <v>0</v>
+      </c>
+      <c r="F284" t="n">
+        <v>0</v>
+      </c>
+      <c r="G284" t="n">
+        <v>0</v>
+      </c>
+      <c r="H284" t="n">
+        <v>0</v>
+      </c>
+      <c r="I284" t="n">
+        <v>0</v>
+      </c>
+      <c r="J284" t="n">
+        <v>0</v>
+      </c>
+      <c r="K284" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>LSC-58</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>0</v>
+      </c>
+      <c r="C285" t="n">
+        <v>0</v>
+      </c>
+      <c r="D285" t="n">
+        <v>0</v>
+      </c>
+      <c r="E285" t="n">
+        <v>0</v>
+      </c>
+      <c r="F285" t="n">
+        <v>0</v>
+      </c>
+      <c r="G285" t="n">
+        <v>0</v>
+      </c>
+      <c r="H285" t="n">
+        <v>0</v>
+      </c>
+      <c r="I285" t="n">
+        <v>0</v>
+      </c>
+      <c r="J285" t="n">
+        <v>0</v>
+      </c>
+      <c r="K285" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>LSC-59</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>0</v>
+      </c>
+      <c r="C286" t="n">
+        <v>0</v>
+      </c>
+      <c r="D286" t="n">
+        <v>0</v>
+      </c>
+      <c r="E286" t="n">
+        <v>0</v>
+      </c>
+      <c r="F286" t="n">
+        <v>0</v>
+      </c>
+      <c r="G286" t="n">
+        <v>0</v>
+      </c>
+      <c r="H286" t="n">
+        <v>0</v>
+      </c>
+      <c r="I286" t="n">
+        <v>0</v>
+      </c>
+      <c r="J286" t="n">
+        <v>0</v>
+      </c>
+      <c r="K286" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>LSC-60</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>0</v>
+      </c>
+      <c r="C287" t="n">
+        <v>0</v>
+      </c>
+      <c r="D287" t="n">
+        <v>0</v>
+      </c>
+      <c r="E287" t="n">
+        <v>0</v>
+      </c>
+      <c r="F287" t="n">
+        <v>0</v>
+      </c>
+      <c r="G287" t="n">
+        <v>0</v>
+      </c>
+      <c r="H287" t="n">
+        <v>0</v>
+      </c>
+      <c r="I287" t="n">
+        <v>0</v>
+      </c>
+      <c r="J287" t="n">
+        <v>0</v>
+      </c>
+      <c r="K287" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>LSC-61</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>0</v>
+      </c>
+      <c r="C288" t="n">
+        <v>0</v>
+      </c>
+      <c r="D288" t="n">
+        <v>0</v>
+      </c>
+      <c r="E288" t="n">
+        <v>0</v>
+      </c>
+      <c r="F288" t="n">
+        <v>0</v>
+      </c>
+      <c r="G288" t="n">
+        <v>0</v>
+      </c>
+      <c r="H288" t="n">
+        <v>0</v>
+      </c>
+      <c r="I288" t="n">
+        <v>0</v>
+      </c>
+      <c r="J288" t="n">
+        <v>0</v>
+      </c>
+      <c r="K288" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>LSC-62</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>0</v>
+      </c>
+      <c r="C289" t="n">
+        <v>0</v>
+      </c>
+      <c r="D289" t="n">
+        <v>0</v>
+      </c>
+      <c r="E289" t="n">
+        <v>0</v>
+      </c>
+      <c r="F289" t="n">
+        <v>0</v>
+      </c>
+      <c r="G289" t="n">
+        <v>0</v>
+      </c>
+      <c r="H289" t="n">
+        <v>0</v>
+      </c>
+      <c r="I289" t="n">
+        <v>0</v>
+      </c>
+      <c r="J289" t="n">
+        <v>0</v>
+      </c>
+      <c r="K289" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>SCR-08</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>0</v>
+      </c>
+      <c r="C290" t="n">
+        <v>0</v>
+      </c>
+      <c r="D290" t="n">
+        <v>0</v>
+      </c>
+      <c r="E290" t="n">
+        <v>0</v>
+      </c>
+      <c r="F290" t="n">
+        <v>0</v>
+      </c>
+      <c r="G290" t="n">
+        <v>0</v>
+      </c>
+      <c r="H290" t="n">
+        <v>0</v>
+      </c>
+      <c r="I290" t="n">
+        <v>0</v>
+      </c>
+      <c r="J290" t="n">
+        <v>0</v>
+      </c>
+      <c r="K290" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>LSC-63</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>0</v>
+      </c>
+      <c r="C291" t="n">
+        <v>0</v>
+      </c>
+      <c r="D291" t="n">
+        <v>0</v>
+      </c>
+      <c r="E291" t="n">
+        <v>0</v>
+      </c>
+      <c r="F291" t="n">
+        <v>0</v>
+      </c>
+      <c r="G291" t="n">
+        <v>0</v>
+      </c>
+      <c r="H291" t="n">
+        <v>6.681902749466157</v>
+      </c>
+      <c r="I291" t="n">
+        <v>0</v>
+      </c>
+      <c r="J291" t="n">
+        <v>0</v>
+      </c>
+      <c r="K291" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>DR-144</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>0</v>
+      </c>
+      <c r="C292" t="n">
+        <v>0</v>
+      </c>
+      <c r="D292" t="n">
+        <v>0</v>
+      </c>
+      <c r="E292" t="n">
+        <v>0</v>
+      </c>
+      <c r="F292" t="n">
+        <v>0</v>
+      </c>
+      <c r="G292" t="n">
+        <v>0</v>
+      </c>
+      <c r="H292" t="n">
+        <v>0</v>
+      </c>
+      <c r="I292" t="n">
+        <v>0</v>
+      </c>
+      <c r="J292" t="n">
+        <v>0</v>
+      </c>
+      <c r="K292" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>DR-145</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>0</v>
+      </c>
+      <c r="C293" t="n">
+        <v>0</v>
+      </c>
+      <c r="D293" t="n">
+        <v>0</v>
+      </c>
+      <c r="E293" t="n">
+        <v>0</v>
+      </c>
+      <c r="F293" t="n">
+        <v>0</v>
+      </c>
+      <c r="G293" t="n">
+        <v>0</v>
+      </c>
+      <c r="H293" t="n">
+        <v>0</v>
+      </c>
+      <c r="I293" t="n">
+        <v>0</v>
+      </c>
+      <c r="J293" t="n">
+        <v>0</v>
+      </c>
+      <c r="K293" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>DR-146</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>0</v>
+      </c>
+      <c r="C294" t="n">
+        <v>0</v>
+      </c>
+      <c r="D294" t="n">
+        <v>0</v>
+      </c>
+      <c r="E294" t="n">
+        <v>0</v>
+      </c>
+      <c r="F294" t="n">
+        <v>0</v>
+      </c>
+      <c r="G294" t="n">
+        <v>5.740685340517458</v>
+      </c>
+      <c r="H294" t="n">
+        <v>5.833259838663818</v>
+      </c>
+      <c r="I294" t="n">
+        <v>0</v>
+      </c>
+      <c r="J294" t="n">
+        <v>22.66026809938682</v>
+      </c>
+      <c r="K294" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>DR-147</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>0</v>
+      </c>
+      <c r="C295" t="n">
+        <v>0</v>
+      </c>
+      <c r="D295" t="n">
+        <v>0</v>
+      </c>
+      <c r="E295" t="n">
+        <v>0</v>
+      </c>
+      <c r="F295" t="n">
+        <v>0</v>
+      </c>
+      <c r="G295" t="n">
+        <v>6.552707723218681</v>
+      </c>
+      <c r="H295" t="n">
+        <v>7.256476420011278</v>
+      </c>
+      <c r="I295" t="n">
+        <v>10.78009929167267</v>
+      </c>
+      <c r="J295" t="n">
+        <v>0</v>
+      </c>
+      <c r="K295" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>DR-148</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>6.988924732145268</v>
+      </c>
+      <c r="C296" t="n">
+        <v>5.757897275492518</v>
+      </c>
+      <c r="D296" t="n">
+        <v>0</v>
+      </c>
+      <c r="E296" t="n">
+        <v>14.92069081914642</v>
+      </c>
+      <c r="F296" t="n">
+        <v>13.08557375006232</v>
+      </c>
+      <c r="G296" t="n">
+        <v>26.6344660655082</v>
+      </c>
+      <c r="H296" t="n">
+        <v>99.99999754550056</v>
+      </c>
+      <c r="I296" t="n">
+        <v>12.47105442941014</v>
+      </c>
+      <c r="J296" t="n">
+        <v>76.63822623815099</v>
+      </c>
+      <c r="K296" t="n">
+        <v>6.979213733923796</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>DR-149</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>0</v>
+      </c>
+      <c r="C297" t="n">
+        <v>0</v>
+      </c>
+      <c r="D297" t="n">
+        <v>0</v>
+      </c>
+      <c r="E297" t="n">
+        <v>0</v>
+      </c>
+      <c r="F297" t="n">
+        <v>0</v>
+      </c>
+      <c r="G297" t="n">
+        <v>5.327838802008446</v>
+      </c>
+      <c r="H297" t="n">
+        <v>0</v>
+      </c>
+      <c r="I297" t="n">
+        <v>0</v>
+      </c>
+      <c r="J297" t="n">
+        <v>0</v>
+      </c>
+      <c r="K297" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>DR-150</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>7.262820876455278</v>
+      </c>
+      <c r="C298" t="n">
+        <v>0</v>
+      </c>
+      <c r="D298" t="n">
+        <v>0</v>
+      </c>
+      <c r="E298" t="n">
+        <v>0</v>
+      </c>
+      <c r="F298" t="n">
+        <v>0</v>
+      </c>
+      <c r="G298" t="n">
+        <v>7.132729141377689</v>
+      </c>
+      <c r="H298" t="n">
+        <v>13.95706888936943</v>
+      </c>
+      <c r="I298" t="n">
+        <v>12.62073359058132</v>
+      </c>
+      <c r="J298" t="n">
+        <v>0</v>
+      </c>
+      <c r="K298" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>0</v>
+      </c>
+      <c r="C299" t="n">
+        <v>0</v>
+      </c>
+      <c r="D299" t="n">
+        <v>0</v>
+      </c>
+      <c r="E299" t="n">
+        <v>0</v>
+      </c>
+      <c r="F299" t="n">
+        <v>0</v>
+      </c>
+      <c r="G299" t="n">
+        <v>0</v>
+      </c>
+      <c r="H299" t="n">
+        <v>0</v>
+      </c>
+      <c r="I299" t="n">
+        <v>0</v>
+      </c>
+      <c r="J299" t="n">
+        <v>0</v>
+      </c>
+      <c r="K299" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>DR-151</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>0</v>
+      </c>
+      <c r="C300" t="n">
+        <v>8.594946353211522</v>
+      </c>
+      <c r="D300" t="n">
+        <v>0</v>
+      </c>
+      <c r="E300" t="n">
+        <v>0</v>
+      </c>
+      <c r="F300" t="n">
+        <v>19.08736886554397</v>
+      </c>
+      <c r="G300" t="n">
+        <v>84.4279250692869</v>
+      </c>
+      <c r="H300" t="n">
+        <v>10.6402502289721</v>
+      </c>
+      <c r="I300" t="n">
+        <v>22.79647838284913</v>
+      </c>
+      <c r="J300" t="n">
+        <v>78.30960864053299</v>
+      </c>
+      <c r="K300" t="n">
+        <v>24.85533963257184</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>DR-152</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>0</v>
+      </c>
+      <c r="C301" t="n">
+        <v>0</v>
+      </c>
+      <c r="D301" t="n">
+        <v>0</v>
+      </c>
+      <c r="E301" t="n">
+        <v>0</v>
+      </c>
+      <c r="F301" t="n">
+        <v>0</v>
+      </c>
+      <c r="G301" t="n">
+        <v>5.83504792787634</v>
+      </c>
+      <c r="H301" t="n">
+        <v>0</v>
+      </c>
+      <c r="I301" t="n">
+        <v>15.15717672903713</v>
+      </c>
+      <c r="J301" t="n">
+        <v>0</v>
+      </c>
+      <c r="K301" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>DR-154</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>0</v>
+      </c>
+      <c r="C302" t="n">
+        <v>0</v>
+      </c>
+      <c r="D302" t="n">
+        <v>0</v>
+      </c>
+      <c r="E302" t="n">
+        <v>0</v>
+      </c>
+      <c r="F302" t="n">
+        <v>0</v>
+      </c>
+      <c r="G302" t="n">
+        <v>5.98284898440956</v>
+      </c>
+      <c r="H302" t="n">
+        <v>9.378923733705561</v>
+      </c>
+      <c r="I302" t="n">
+        <v>6.892093174697115</v>
+      </c>
+      <c r="J302" t="n">
+        <v>0</v>
+      </c>
+      <c r="K302" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>DR-155</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>0</v>
+      </c>
+      <c r="C303" t="n">
+        <v>0</v>
+      </c>
+      <c r="D303" t="n">
+        <v>0</v>
+      </c>
+      <c r="E303" t="n">
+        <v>0</v>
+      </c>
+      <c r="F303" t="n">
+        <v>0</v>
+      </c>
+      <c r="G303" t="n">
+        <v>0</v>
+      </c>
+      <c r="H303" t="n">
+        <v>5.091373116196439</v>
+      </c>
+      <c r="I303" t="n">
+        <v>0</v>
+      </c>
+      <c r="J303" t="n">
+        <v>0</v>
+      </c>
+      <c r="K303" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>DR-156</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>0</v>
+      </c>
+      <c r="C304" t="n">
+        <v>0</v>
+      </c>
+      <c r="D304" t="n">
+        <v>0</v>
+      </c>
+      <c r="E304" t="n">
+        <v>0</v>
+      </c>
+      <c r="F304" t="n">
+        <v>0</v>
+      </c>
+      <c r="G304" t="n">
+        <v>0</v>
+      </c>
+      <c r="H304" t="n">
+        <v>0</v>
+      </c>
+      <c r="I304" t="n">
+        <v>0</v>
+      </c>
+      <c r="J304" t="n">
+        <v>0</v>
+      </c>
+      <c r="K304" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>DR-157</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>0</v>
+      </c>
+      <c r="C305" t="n">
+        <v>0</v>
+      </c>
+      <c r="D305" t="n">
+        <v>0</v>
+      </c>
+      <c r="E305" t="n">
+        <v>0</v>
+      </c>
+      <c r="F305" t="n">
+        <v>0</v>
+      </c>
+      <c r="G305" t="n">
+        <v>0</v>
+      </c>
+      <c r="H305" t="n">
+        <v>0</v>
+      </c>
+      <c r="I305" t="n">
+        <v>0</v>
+      </c>
+      <c r="J305" t="n">
+        <v>0</v>
+      </c>
+      <c r="K305" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>DR-158</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>0</v>
+      </c>
+      <c r="C306" t="n">
+        <v>0</v>
+      </c>
+      <c r="D306" t="n">
+        <v>0</v>
+      </c>
+      <c r="E306" t="n">
+        <v>14.03463143926563</v>
+      </c>
+      <c r="F306" t="n">
+        <v>12.09844426801691</v>
+      </c>
+      <c r="G306" t="n">
+        <v>9.775918907971436</v>
+      </c>
+      <c r="H306" t="n">
+        <v>10.32008274953751</v>
+      </c>
+      <c r="I306" t="n">
+        <v>27.88032223917946</v>
+      </c>
+      <c r="J306" t="n">
+        <v>6.88604263071726</v>
+      </c>
+      <c r="K306" t="n">
+        <v>11.99230886438421</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>DR-159</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>0</v>
+      </c>
+      <c r="C307" t="n">
+        <v>0</v>
+      </c>
+      <c r="D307" t="n">
+        <v>0</v>
+      </c>
+      <c r="E307" t="n">
+        <v>0</v>
+      </c>
+      <c r="F307" t="n">
+        <v>0</v>
+      </c>
+      <c r="G307" t="n">
+        <v>0</v>
+      </c>
+      <c r="H307" t="n">
+        <v>5.405775384698827</v>
+      </c>
+      <c r="I307" t="n">
+        <v>0</v>
+      </c>
+      <c r="J307" t="n">
+        <v>0</v>
+      </c>
+      <c r="K307" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>LSC-64</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>0</v>
+      </c>
+      <c r="C308" t="n">
+        <v>0</v>
+      </c>
+      <c r="D308" t="n">
+        <v>0</v>
+      </c>
+      <c r="E308" t="n">
+        <v>0</v>
+      </c>
+      <c r="F308" t="n">
+        <v>0</v>
+      </c>
+      <c r="G308" t="n">
+        <v>0</v>
+      </c>
+      <c r="H308" t="n">
+        <v>29.60315858123303</v>
+      </c>
+      <c r="I308" t="n">
+        <v>0</v>
+      </c>
+      <c r="J308" t="n">
+        <v>0</v>
+      </c>
+      <c r="K308" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>LSC-65</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>0</v>
+      </c>
+      <c r="C309" t="n">
+        <v>0</v>
+      </c>
+      <c r="D309" t="n">
+        <v>0</v>
+      </c>
+      <c r="E309" t="n">
+        <v>0</v>
+      </c>
+      <c r="F309" t="n">
+        <v>0</v>
+      </c>
+      <c r="G309" t="n">
+        <v>0</v>
+      </c>
+      <c r="H309" t="n">
+        <v>19.56039334862705</v>
+      </c>
+      <c r="I309" t="n">
+        <v>0</v>
+      </c>
+      <c r="J309" t="n">
+        <v>0</v>
+      </c>
+      <c r="K309" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>LSC-66</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>0</v>
+      </c>
+      <c r="C310" t="n">
+        <v>0</v>
+      </c>
+      <c r="D310" t="n">
+        <v>0</v>
+      </c>
+      <c r="E310" t="n">
+        <v>0</v>
+      </c>
+      <c r="F310" t="n">
+        <v>0</v>
+      </c>
+      <c r="G310" t="n">
+        <v>0</v>
+      </c>
+      <c r="H310" t="n">
+        <v>6.292300746884432</v>
+      </c>
+      <c r="I310" t="n">
+        <v>0</v>
+      </c>
+      <c r="J310" t="n">
+        <v>0</v>
+      </c>
+      <c r="K310" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>LSC-67</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>0</v>
+      </c>
+      <c r="C311" t="n">
+        <v>0</v>
+      </c>
+      <c r="D311" t="n">
+        <v>0</v>
+      </c>
+      <c r="E311" t="n">
+        <v>0</v>
+      </c>
+      <c r="F311" t="n">
+        <v>0</v>
+      </c>
+      <c r="G311" t="n">
+        <v>0</v>
+      </c>
+      <c r="H311" t="n">
         <v>32.10045861871748</v>
       </c>
-      <c r="I234" t="n">
-        <v>0</v>
-      </c>
-      <c r="J234" t="n">
-        <v>0</v>
-      </c>
-      <c r="K234" t="n">
+      <c r="I311" t="n">
+        <v>0</v>
+      </c>
+      <c r="J311" t="n">
+        <v>0</v>
+      </c>
+      <c r="K311" t="n">
         <v>0</v>
       </c>
     </row>
